--- a/data/metadata/lqas_metadata.xlsx
+++ b/data/metadata/lqas_metadata.xlsx
@@ -423,7 +423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-19 16:50:22</t>
+          <t>2026-06-04 09:40:42</t>
         </is>
       </c>
     </row>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-19 16:50:22</t>
+          <t>2026-06-04 09:40:42</t>
         </is>
       </c>
     </row>

--- a/data/metadata/lqas_metadata.xlsx
+++ b/data/metadata/lqas_metadata.xlsx
@@ -423,7 +423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04 09:40:42</t>
+          <t>2026-06-10 09:54:28</t>
         </is>
       </c>
     </row>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04 09:40:42</t>
+          <t>2026-06-10 09:54:28</t>
         </is>
       </c>
     </row>

--- a/data/metadata/lqas_metadata.xlsx
+++ b/data/metadata/lqas_metadata.xlsx
@@ -423,7 +423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-10 09:54:28</t>
+          <t>2026-06-11 13:06:20</t>
         </is>
       </c>
     </row>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-10 09:54:28</t>
+          <t>2026-06-11 13:06:20</t>
         </is>
       </c>
     </row>

--- a/data/metadata/lqas_metadata.xlsx
+++ b/data/metadata/lqas_metadata.xlsx
@@ -423,7 +423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-11 13:06:20</t>
+          <t>2026-06-17 10:04:19</t>
         </is>
       </c>
     </row>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-11 13:06:20</t>
+          <t>2026-06-17 10:04:19</t>
         </is>
       </c>
     </row>

--- a/data/metadata/lqas_metadata.xlsx
+++ b/data/metadata/lqas_metadata.xlsx
@@ -423,7 +423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-17 10:04:19</t>
+          <t>2026-08-15 16:32:42</t>
         </is>
       </c>
     </row>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>31507</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ANGOLA-NID-2024-nOPV2</t>
+          <t>ANG-2026-03-01_nOPV_NID</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rnd1</t>
+          <t>Rnd2</t>
         </is>
       </c>
       <c r="F7">
@@ -836,23 +836,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rnd2</t>
+          <t>Rnd1</t>
         </is>
       </c>
       <c r="F8">
         <v>60</v>
       </c>
       <c r="G8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J8">
@@ -872,24 +872,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BARRA DO DANDE</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ANG-2025-08-01_nOPV-NID</t>
+          <t>ANGOLA-NID-2024-nOPV2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rnd1</t>
+          <t>Rnd2</t>
         </is>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="J9">
@@ -928,23 +928,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rnd2</t>
+          <t>Rnd1</t>
         </is>
       </c>
       <c r="F10">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G10">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="J10">
@@ -969,12 +969,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ANG-2026-03-01_nOPV_NID</t>
+          <t>ANG-2025-08-01_nOPV-NID</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rnd1</t>
+          <t>Rnd2</t>
         </is>
       </c>
       <c r="F11">
@@ -1097,16 +1097,16 @@
         <v>45186</v>
       </c>
       <c r="E3" s="2">
-        <v>46113</v>
+        <v>46169</v>
       </c>
       <c r="F3">
-        <v>89.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="G3">
-        <v>57.8</v>
+        <v>61.5</v>
       </c>
       <c r="H3">
-        <v>1781</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="4">
@@ -1125,16 +1125,16 @@
         <v>43893</v>
       </c>
       <c r="E4" s="2">
-        <v>46141</v>
+        <v>46192</v>
       </c>
       <c r="F4">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G4">
-        <v>69.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H4">
-        <v>430</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -1209,16 +1209,16 @@
         <v>44984</v>
       </c>
       <c r="E7" s="2">
-        <v>46152</v>
+        <v>46195</v>
       </c>
       <c r="F7">
-        <v>88.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="G7">
-        <v>54.8</v>
+        <v>53.4</v>
       </c>
       <c r="H7">
-        <v>84</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8">
@@ -1237,16 +1237,16 @@
         <v>44084</v>
       </c>
       <c r="E8" s="2">
-        <v>46140</v>
+        <v>46182</v>
       </c>
       <c r="F8">
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="G8">
-        <v>65.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H8">
-        <v>2267</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="9">
@@ -1265,16 +1265,16 @@
         <v>43867</v>
       </c>
       <c r="E9" s="2">
-        <v>46148</v>
+        <v>46183</v>
       </c>
       <c r="F9">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G9">
-        <v>75.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H9">
-        <v>2073</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="10">
@@ -1343,22 +1343,22 @@
         <v>211</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="2">
         <v>44490</v>
       </c>
       <c r="E12" s="2">
-        <v>46159</v>
+        <v>46201</v>
       </c>
       <c r="F12">
         <v>96.3</v>
       </c>
       <c r="G12">
-        <v>61</v>
+        <v>61.3</v>
       </c>
       <c r="H12">
-        <v>638</v>
+        <v>651</v>
       </c>
     </row>
     <row r="13">
@@ -1427,22 +1427,22 @@
         <v>38</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2">
         <v>44053</v>
       </c>
       <c r="E15" s="2">
-        <v>45790</v>
+        <v>46199</v>
       </c>
       <c r="F15">
-        <v>91.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G15">
-        <v>66.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="H15">
-        <v>330</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16">
@@ -1573,16 +1573,16 @@
         <v>44565</v>
       </c>
       <c r="E20" s="2">
-        <v>46147</v>
+        <v>46197</v>
       </c>
       <c r="F20">
-        <v>90.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G20">
-        <v>52.9</v>
+        <v>55.4</v>
       </c>
       <c r="H20">
-        <v>240</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21">
@@ -1601,16 +1601,16 @@
         <v>44565</v>
       </c>
       <c r="E21" s="2">
-        <v>45965</v>
+        <v>46232</v>
       </c>
       <c r="F21">
-        <v>92.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G21">
-        <v>69.8</v>
+        <v>68</v>
       </c>
       <c r="H21">
-        <v>1458</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="22">
@@ -1629,16 +1629,16 @@
         <v>46010</v>
       </c>
       <c r="E22" s="2">
-        <v>46144</v>
+        <v>46186</v>
       </c>
       <c r="F22">
-        <v>92.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="G22">
-        <v>63.7</v>
+        <v>64.3</v>
       </c>
       <c r="H22">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23">
@@ -1657,16 +1657,16 @@
         <v>43845</v>
       </c>
       <c r="E23" s="2">
-        <v>46156</v>
+        <v>46242</v>
       </c>
       <c r="F23">
         <v>97.09999999999999</v>
       </c>
       <c r="G23">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="H23">
-        <v>7955</v>
+        <v>7977</v>
       </c>
     </row>
     <row r="24">
@@ -1685,16 +1685,16 @@
         <v>44101</v>
       </c>
       <c r="E24" s="2">
-        <v>46141</v>
+        <v>46183</v>
       </c>
       <c r="F24">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="G24">
-        <v>87.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H24">
-        <v>809</v>
+        <v>870</v>
       </c>
     </row>
     <row r="25">
@@ -1704,25 +1704,25 @@
         </is>
       </c>
       <c r="B25">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C25">
         <v>11</v>
       </c>
       <c r="D25" s="2">
-        <v>44152</v>
+        <v>44055</v>
       </c>
       <c r="E25" s="2">
-        <v>46129</v>
+        <v>46234</v>
       </c>
       <c r="F25">
         <v>95.7</v>
       </c>
       <c r="G25">
-        <v>75.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H25">
-        <v>367</v>
+        <v>389</v>
       </c>
     </row>
     <row r="26">
@@ -1732,25 +1732,25 @@
         </is>
       </c>
       <c r="B26">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2">
-        <v>44956</v>
+        <v>45635</v>
       </c>
       <c r="E26" s="2">
-        <v>46056</v>
+        <v>46362</v>
       </c>
       <c r="F26">
-        <v>97.2</v>
+        <v>98</v>
       </c>
       <c r="G26">
-        <v>78.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H26">
-        <v>5006</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="27">
@@ -1844,16 +1844,16 @@
         </is>
       </c>
       <c r="B30">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2">
         <v>44149</v>
       </c>
       <c r="E30" s="2">
-        <v>46154</v>
+        <v>46219</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="G30">
-        <v>45.1</v>
+        <v>46.9</v>
       </c>
       <c r="H30">
-        <v>288</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C34">
         <v>5</v>
@@ -1967,16 +1967,16 @@
         <v>44860</v>
       </c>
       <c r="E34" s="2">
-        <v>46137</v>
+        <v>46217</v>
       </c>
       <c r="F34">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G34">
-        <v>66.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H34">
-        <v>619</v>
+        <v>676</v>
       </c>
     </row>
     <row r="35">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -1995,16 +1995,16 @@
         <v>43834</v>
       </c>
       <c r="E35" s="2">
-        <v>46137</v>
+        <v>46236</v>
       </c>
       <c r="F35">
-        <v>96.09999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="G35">
-        <v>77.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H35">
-        <v>883</v>
+        <v>1024</v>
       </c>
     </row>
   </sheetData>
@@ -2729,24 +2729,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>nc_reason_covid_19</t>
+          <t>prct_r_non_compliance</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Count of children with specific non-compliance reason</t>
+          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>prct_r_non_compliance</t>
+          <t>prct_r_house_not_visited</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>prct_r_house_not_visited</t>
+          <t>prct_r_childabsent</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>prct_r_childabsent</t>
+          <t>prct_r_Child_was_asleep</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2797,7 +2797,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>prct_r_Child_was_asleep</t>
+          <t>prct_r_Child_is_a_visitor</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2814,7 +2814,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>prct_r_Child_is_a_visitor</t>
+          <t>prct_r_Vaccinated_but_not_FM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>prct_r_Vaccinated_but_not_FM</t>
+          <t>prct_other_r</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>prct_other_r</t>
+          <t>proportion_missed_child</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2856,26 +2856,26 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Proportion of missed children relative to total sampled</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>proportion_missed_child</t>
+          <t>nc_reason_covid_19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Proportion of missed children relative to total sampled</t>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Count of children with specific non-compliance reason</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>31507</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>518</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>706</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>30451</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>208</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>17.35</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-12-06</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2528</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3361,7 +3361,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHD-2026-02_nOPV_NID</t>
+          <t>CHD-2026-02_nOPV_sNID</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3451,22 +3451,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DRC-NID-01-2024-bOPV</t>
+          <t>EXNORD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C10">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>60</v>
       </c>
       <c r="E10">
-        <v>99.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -3481,7 +3481,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXNORD</t>
+          <t>KEN-2024-01-01_nOPV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3490,13 +3490,13 @@
         </is>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>60</v>
       </c>
       <c r="E11">
-        <v>96.7</v>
+        <v>99.8</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -3511,7 +3511,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KEN-2024-01-01_nOPV</t>
+          <t>MopUp2022_nOPV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3520,13 +3520,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <v>60</v>
       </c>
       <c r="E12">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -3541,7 +3541,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MopUp2022_nOPV</t>
+          <t>NIG-2023-11-01_nOPV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3556,7 +3556,7 @@
         <v>60</v>
       </c>
       <c r="E13">
-        <v>99</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -3571,7 +3571,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NIG-2023-11-01_nOPV</t>
+          <t>TNZ-2023-07-01_nOPV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3580,13 +3580,13 @@
         </is>
       </c>
       <c r="C14">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="D14">
         <v>60</v>
       </c>
       <c r="E14">
-        <v>97.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -3601,7 +3601,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TNZ-2023-07-01_nOPV</t>
+          <t>nOPV2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="C15">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>60</v>
       </c>
       <c r="E15">
-        <v>99.90000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -3631,7 +3631,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nOPV2023</t>
+          <t>BEN-2025-11-01_nOPV_sNID</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3640,19 +3640,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="D16">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="E16">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="F16">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="G16">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -3661,7 +3661,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BEN-2025-11-01_nOPV_sNID</t>
+          <t>GUI-2025-01-NID_bOPV-nOPV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3670,19 +3670,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D17">
         <v>60</v>
       </c>
       <c r="E17">
-        <v>98.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="F17">
-        <v>97.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="G17">
-        <v>97.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GUI-2025-01-NID_bOPV-nOPV</t>
+          <t>BFA-2025-08-01_nOPV_sNIDs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3700,19 +3700,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="D18">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="E18">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="F18">
-        <v>97.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="G18">
-        <v>97.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BFA-2025-08-01_nOPV_sNIDs</t>
+          <t>DRC-2026-01-01_nOPV_sNID</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3730,19 +3730,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>60</v>
       </c>
       <c r="E19">
-        <v>98.7</v>
+        <v>98.2</v>
       </c>
       <c r="F19">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G19">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -3841,7 +3841,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALG-2024-01-01_nOPV</t>
+          <t>DRC-2026-02-bOPV-nOPV_sNID</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D23">
-        <v>60</v>
+        <v>58.9</v>
       </c>
       <c r="E23">
-        <v>98.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F23">
-        <v>94.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G23">
-        <v>94.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3871,7 +3871,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nVPO_Zinder</t>
+          <t>ALG-2024-01-01_nOPV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3880,19 +3880,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>60</v>
       </c>
       <c r="E24">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="F24">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="G24">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -3901,7 +3901,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CAM-2024-sNID-01_nOPV</t>
+          <t>nVPO_Zinder</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3910,19 +3910,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="D25">
         <v>60</v>
       </c>
       <c r="E25">
-        <v>97.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F25">
-        <v>93.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G25">
-        <v>93.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3931,7 +3931,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHD-2023-05-1_nOPV</t>
+          <t>CAM-2024-sNID-01_nOPV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3940,19 +3940,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="D26">
-        <v>59.8</v>
+        <v>60</v>
       </c>
       <c r="E26">
-        <v>97.7</v>
+        <v>97.5</v>
       </c>
       <c r="F26">
-        <v>92.5</v>
+        <v>93.2</v>
       </c>
       <c r="G26">
-        <v>92.5</v>
+        <v>93.2</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3961,7 +3961,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GUI-2024-10-NID_nOPV</t>
+          <t>CHD-2023-05-1_nOPV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3970,19 +3970,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>38</v>
+        <v>226</v>
       </c>
       <c r="D27">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="E27">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="F27">
-        <v>92.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="G27">
-        <v>92.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BEN-2025-04-01_nOPV_NIDs</t>
+          <t>GUI-2024-10-NID_nOPV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4000,19 +4000,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="D28">
         <v>60</v>
       </c>
       <c r="E28">
-        <v>98.09999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="F28">
-        <v>91.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G28">
-        <v>91.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -4021,7 +4021,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DRC-2024-10-01_B_nOPV</t>
+          <t>BEN-2025-04-01_nOPV_NIDs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4030,19 +4030,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>882</v>
+        <v>172</v>
       </c>
       <c r="D29">
-        <v>59.3</v>
+        <v>60</v>
       </c>
       <c r="E29">
         <v>98.09999999999999</v>
       </c>
       <c r="F29">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G29">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -4161,7 +4161,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BFA-2024-02-01_nOPV</t>
+          <t>ZAM-2026-03-01_nOPV-sNID</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4170,19 +4170,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="D34">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="E34">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F34">
-        <v>91.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="G34">
-        <v>91.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -4191,7 +4191,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DRC-2024-sNIDs_nOPV</t>
+          <t>BFA-2024-02-01_nOPV</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4200,19 +4200,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D35">
         <v>60</v>
       </c>
       <c r="E35">
-        <v>97.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F35">
-        <v>90.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="G35">
-        <v>90.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DRC-sNID-08-2024-B_nOPV</t>
+          <t>DRC-2025-06-01_nOPV_NID</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4230,19 +4230,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>122</v>
+        <v>393</v>
       </c>
       <c r="D36">
-        <v>59.3</v>
+        <v>59.5</v>
       </c>
       <c r="E36">
         <v>97.90000000000001</v>
       </c>
       <c r="F36">
-        <v>90.2</v>
+        <v>90.8</v>
       </c>
       <c r="G36">
-        <v>90.2</v>
+        <v>90.8</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -4251,7 +4251,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NIE-2025-04-01_nOPV_NIDs</t>
+          <t>DRC-2026-03-NID_bOPV-nOPV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4260,28 +4260,28 @@
         </is>
       </c>
       <c r="C37">
-        <v>1030</v>
+        <v>838</v>
       </c>
       <c r="D37">
-        <v>60.1</v>
+        <v>59.1</v>
       </c>
       <c r="E37">
-        <v>97.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F37">
-        <v>90.2</v>
+        <v>90.7</v>
       </c>
       <c r="G37">
-        <v>90.2</v>
+        <v>90.7</v>
       </c>
       <c r="H37">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CIV-2024-04-01_nOPV</t>
+          <t>NIE-2025-04-01_nOPV_NIDs</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4290,49 +4290,49 @@
         </is>
       </c>
       <c r="C38">
-        <v>159</v>
+        <v>1030</v>
       </c>
       <c r="D38">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="E38">
-        <v>97.3</v>
+        <v>97.8</v>
       </c>
       <c r="F38">
-        <v>89.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="G38">
-        <v>89.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ouagadogou-mOPV2</t>
+          <t>CIV-2024-04-01_nOPV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C39">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="D39">
         <v>60</v>
       </c>
       <c r="E39">
-        <v>97</v>
+        <v>97.3</v>
       </c>
       <c r="F39">
-        <v>89.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G39">
-        <v>89.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -4341,28 +4341,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NIG-2024-10-01_nOPV</t>
+          <t>Ouagadogou-mOPV2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>mOPV</t>
         </is>
       </c>
       <c r="C40">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D40">
         <v>60</v>
       </c>
       <c r="E40">
-        <v>97.2</v>
+        <v>97</v>
       </c>
       <c r="F40">
-        <v>89.3</v>
+        <v>89.7</v>
       </c>
       <c r="G40">
-        <v>89.3</v>
+        <v>89.7</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DRC-2023-11-02_nOPV</t>
+          <t>NIG-2024-10-01_nOPV</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4380,19 +4380,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>424</v>
+        <v>122</v>
       </c>
       <c r="D41">
-        <v>59.8</v>
+        <v>60</v>
       </c>
       <c r="E41">
         <v>97.2</v>
       </c>
       <c r="F41">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="G41">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -4401,7 +4401,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DRC-2025-06-01_nOPV_NID</t>
+          <t>CAM-2023-05-01_nOPV</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4410,19 +4410,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>396</v>
+        <v>146</v>
       </c>
       <c r="D42">
         <v>60</v>
       </c>
       <c r="E42">
-        <v>97.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="F42">
-        <v>89.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="G42">
-        <v>89.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CAM-2023-05-01_nOPV</t>
+          <t>MOZ-2024-04-01_bOPV</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C43">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="D43">
         <v>60</v>
       </c>
       <c r="E43">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F43">
         <v>89</v>
@@ -4461,28 +4461,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MOZ-2024-04-01_bOPV</t>
+          <t>Chavuma-mOPV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>mOPV</t>
         </is>
       </c>
       <c r="C44">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="D44">
-        <v>60</v>
+        <v>58.9</v>
       </c>
       <c r="E44">
-        <v>97.09999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F44">
-        <v>89</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G44">
-        <v>89</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -4491,22 +4491,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chavuma-mOPV</t>
+          <t>DRC-2025-02-01_nOPV_sNID</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>mOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C45">
-        <v>9</v>
+        <v>217</v>
       </c>
       <c r="D45">
-        <v>58.9</v>
+        <v>59.4</v>
       </c>
       <c r="E45">
-        <v>99.59999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F45">
         <v>88.90000000000001</v>
@@ -4593,7 +4593,7 @@
         <v>228</v>
       </c>
       <c r="D48">
-        <v>60.1</v>
+        <v>60.2</v>
       </c>
       <c r="E48">
         <v>96.8</v>
@@ -4701,7 +4701,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DRC-2025-02-01_nOPV_sNID</t>
+          <t>ZAM-2023-09-01_nOPV</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="C52">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="D52">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="E52">
-        <v>97.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F52">
         <v>88.09999999999999</v>
@@ -4731,7 +4731,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ZAM-2023-09-01_nOPV</t>
+          <t>ALG-2025-09-01_nOPV_NID</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4740,19 +4740,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>168</v>
+        <v>548</v>
       </c>
       <c r="D53">
-        <v>60</v>
+        <v>61.1</v>
       </c>
       <c r="E53">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="F53">
-        <v>88.09999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="G53">
-        <v>88.09999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -4761,7 +4761,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ALG-2025-09-01_nOPV_NID</t>
+          <t>CAR-2023-05-01_nOPV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4770,19 +4770,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>548</v>
+        <v>56</v>
       </c>
       <c r="D54">
-        <v>61.1</v>
+        <v>60</v>
       </c>
       <c r="E54">
-        <v>97.7</v>
+        <v>96.3</v>
       </c>
       <c r="F54">
-        <v>87.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="G54">
-        <v>87.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -4791,7 +4791,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CAR-2023-05-01_nOPV</t>
+          <t>ExtNord2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4800,13 +4800,13 @@
         </is>
       </c>
       <c r="C55">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="D55">
         <v>60</v>
       </c>
       <c r="E55">
-        <v>96.3</v>
+        <v>97.5</v>
       </c>
       <c r="F55">
         <v>87.5</v>
@@ -4821,7 +4821,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ExtNord2023</t>
+          <t>RCA-2026-03_nOPV_sNID</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4830,13 +4830,13 @@
         </is>
       </c>
       <c r="C56">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D56">
-        <v>60</v>
+        <v>59.6</v>
       </c>
       <c r="E56">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="F56">
         <v>87.5</v>
@@ -4881,22 +4881,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NIE-2023-07-03_nOPV</t>
+          <t>DRC-2025-11-01_n-BOPV_sNID</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C58">
-        <v>728</v>
+        <v>406</v>
       </c>
       <c r="D58">
-        <v>59.4</v>
+        <v>58.3</v>
       </c>
       <c r="E58">
-        <v>97.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="F58">
         <v>86</v>
@@ -4905,13 +4905,13 @@
         <v>86</v>
       </c>
       <c r="H58">
-        <v>87.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>NIE-2023-07-03_nOPV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4920,49 +4920,49 @@
         </is>
       </c>
       <c r="C59">
-        <v>774</v>
+        <v>728</v>
       </c>
       <c r="D59">
-        <v>61.9</v>
+        <v>59.4</v>
       </c>
       <c r="E59">
         <v>97.59999999999999</v>
       </c>
       <c r="F59">
-        <v>85.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="G59">
-        <v>85.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="H59">
-        <v>87.5</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CHD-2025-10-0n_bOPV-NIDs</t>
+          <t>DRC-2024-10-01_B_nOPV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C60">
-        <v>357</v>
+        <v>429</v>
       </c>
       <c r="D60">
-        <v>60</v>
+        <v>58.4</v>
       </c>
       <c r="E60">
-        <v>96.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F60">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="G60">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -4971,28 +4971,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NIG-2025-10-01_nOPV_sNID</t>
+          <t>CHD-2025-10-0n_bOPV-NIDs</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C61">
-        <v>46</v>
+        <v>357</v>
       </c>
       <c r="D61">
         <v>60</v>
       </c>
       <c r="E61">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F61">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G61">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -5001,28 +5001,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CNG-2024-08-BOPV</t>
+          <t>NIG-2025-10-01_nOPV_sNID</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C62">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D62">
         <v>60</v>
       </c>
       <c r="E62">
-        <v>95.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F62">
-        <v>84.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="G62">
-        <v>84.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -5031,28 +5031,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CHD-2026-03_nOPV_NID</t>
+          <t>CNG-2024-08-BOPV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C63">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="D63">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="E63">
-        <v>96.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F63">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G63">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -5061,22 +5061,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DRC-2026-01-01_nOPV_sNID</t>
+          <t>ZAM-2023-05-01_bOPV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C64">
-        <v>452</v>
+        <v>116</v>
       </c>
       <c r="D64">
-        <v>72.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="E64">
-        <v>98</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F64">
         <v>84.5</v>
@@ -5091,31 +5091,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ZAM-2023-05-01_bOPV</t>
+          <t>OBR_name</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C65">
-        <v>116</v>
+        <v>796</v>
       </c>
       <c r="D65">
-        <v>60</v>
+        <v>61.6</v>
       </c>
       <c r="E65">
-        <v>97.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F65">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="G65">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="66">
@@ -5163,7 +5163,7 @@
         <v>148</v>
       </c>
       <c r="D67">
-        <v>60.3</v>
+        <v>60</v>
       </c>
       <c r="E67">
         <v>96.09999999999999</v>
@@ -5361,7 +5361,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ETH-2026-03-nOPV2-sNID</t>
+          <t>NIG-2026-03_nOPV_NIDs</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5370,19 +5370,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D74">
-        <v>139.3</v>
+        <v>59.9</v>
       </c>
       <c r="E74">
-        <v>98.5</v>
+        <v>95.3</v>
       </c>
       <c r="F74">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="G74">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -5391,28 +5391,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DRC-NID-04-2024-bOPV</t>
+          <t>ETH-2026-03-nOPV2-sNID</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C75">
-        <v>508</v>
+        <v>108</v>
       </c>
       <c r="D75">
-        <v>59.8</v>
+        <v>139.3</v>
       </c>
       <c r="E75">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="F75">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G75">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -5541,28 +5541,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ZAM-2026-03-01_nOPV-sNID</t>
+          <t>GOTHEYE-mOPV</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>mOPV</t>
         </is>
       </c>
       <c r="C80">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D80">
-        <v>76.3</v>
+        <v>59.6</v>
       </c>
       <c r="E80">
-        <v>97.3</v>
+        <v>95.8</v>
       </c>
       <c r="F80">
-        <v>78.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="G80">
-        <v>78.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -5571,28 +5571,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GOTHEYE-mOPV</t>
+          <t>ANG-2025-05-01_nOPV-sNID</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>mOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C81">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D81">
-        <v>59.6</v>
+        <v>60</v>
       </c>
       <c r="E81">
-        <v>95.8</v>
+        <v>94.7</v>
       </c>
       <c r="F81">
-        <v>78.7</v>
+        <v>78.3</v>
       </c>
       <c r="G81">
-        <v>78.7</v>
+        <v>78.3</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -5601,37 +5601,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ANG-2025-05-01_nOPV-sNID</t>
+          <t>NIE-2023-07-03_nOPV</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>fIPV+nOPV2</t>
         </is>
       </c>
       <c r="C82">
-        <v>46</v>
+        <v>253</v>
       </c>
       <c r="D82">
-        <v>61.3</v>
+        <v>58.4</v>
       </c>
       <c r="E82">
-        <v>94.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F82">
-        <v>78.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G82">
-        <v>78.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CAM-2026-03_nOPV_sNID</t>
+          <t>RCA-2025-10-01_nOPV_NIDs</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5640,19 +5640,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>131</v>
+        <v>63</v>
       </c>
       <c r="D83">
-        <v>60.3</v>
+        <v>60</v>
       </c>
       <c r="E83">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="F83">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="G83">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -5661,37 +5661,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NIE-2023-07-03_nOPV</t>
+          <t>CAR-2024-02-01_nOPV</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>fIPV+nOPV2</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C84">
-        <v>253</v>
+        <v>62</v>
       </c>
       <c r="D84">
-        <v>58.4</v>
+        <v>59.4</v>
       </c>
       <c r="E84">
-        <v>96.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="F84">
-        <v>77.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G84">
-        <v>77.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H84">
-        <v>82.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CAR-2024-02-01_nOPV</t>
+          <t>CAR-2024-sNIDs-11_nOPV</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5700,19 +5700,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D85">
-        <v>59.4</v>
+        <v>57.3</v>
       </c>
       <c r="E85">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="F85">
-        <v>77.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="G85">
-        <v>77.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>66</v>
       </c>
       <c r="D87">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="E87">
         <v>96.2</v>
@@ -5793,7 +5793,7 @@
         <v>13</v>
       </c>
       <c r="D88">
-        <v>63.1</v>
+        <v>60</v>
       </c>
       <c r="E88">
         <v>95.8</v>
@@ -5811,7 +5811,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NIG-2026-03_nOPV_NIDs</t>
+          <t>CAM-2026-03_nOPV_sNID</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5820,19 +5820,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="D89">
-        <v>60.3</v>
+        <v>60</v>
       </c>
       <c r="E89">
-        <v>93.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F89">
-        <v>76.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G89">
-        <v>76.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -5841,28 +5841,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MOZ-2025-05-1_nOPV_NID</t>
+          <t>bOPV Rnd 2 ETH-2026-05-bOPV2-sNID</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C90">
-        <v>320</v>
+        <v>13</v>
       </c>
       <c r="D90">
-        <v>60</v>
+        <v>103.8</v>
       </c>
       <c r="E90">
-        <v>93.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F90">
-        <v>76.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G90">
-        <v>76.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CAM-2025-04-01_nOPV_NIDs</t>
+          <t>ANG-2026-03-01_nOPV_NID</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="C91">
-        <v>325</v>
+        <v>650</v>
       </c>
       <c r="D91">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="E91">
-        <v>94.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F91">
         <v>76</v>
@@ -5901,7 +5901,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ZIM-2023-12-01_nOPV</t>
+          <t>CAM-2025-04-01_nOPV_NIDs</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5910,13 +5910,13 @@
         </is>
       </c>
       <c r="C92">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="D92">
-        <v>59.5</v>
+        <v>60</v>
       </c>
       <c r="E92">
-        <v>95.8</v>
+        <v>94.7</v>
       </c>
       <c r="F92">
         <v>76</v>
@@ -5931,7 +5931,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LBR-2024-05-01_nOPV</t>
+          <t>ZIM-2023-12-01_nOPV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5940,19 +5940,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>291</v>
+        <v>150</v>
       </c>
       <c r="D93">
-        <v>58.9</v>
+        <v>59.5</v>
       </c>
       <c r="E93">
-        <v>95.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="F93">
-        <v>75.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="G93">
-        <v>75.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -5961,28 +5961,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DRC-NID-07-2023-bOPV</t>
+          <t>LBR-2024-05-01_nOPV</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C94">
-        <v>591</v>
+        <v>291</v>
       </c>
       <c r="D94">
-        <v>58.5</v>
+        <v>58.9</v>
       </c>
       <c r="E94">
-        <v>96.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F94">
-        <v>75.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G94">
-        <v>75.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -5991,88 +5991,88 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>MOZ-2025-05-1_nOPV_NID</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C95">
-        <v>2425</v>
+        <v>318</v>
       </c>
       <c r="D95">
-        <v>73</v>
+        <v>59.9</v>
       </c>
       <c r="E95">
-        <v>96.8</v>
+        <v>93</v>
       </c>
       <c r="F95">
-        <v>75.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="G95">
-        <v>75.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="H95">
-        <v>86.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CIV-2023-09-01_nOPV</t>
+          <t>OBR_name</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C96">
-        <v>227</v>
+        <v>2425</v>
       </c>
       <c r="D96">
-        <v>59.6</v>
+        <v>73</v>
       </c>
       <c r="E96">
-        <v>95.3</v>
+        <v>96.8</v>
       </c>
       <c r="F96">
-        <v>74.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G96">
-        <v>74.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MDG-2023-03-01_bOPV</t>
+          <t>CAR-2024-sNIDs-09_nOPV</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>mOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C97">
-        <v>452</v>
+        <v>8</v>
       </c>
       <c r="D97">
-        <v>58.4</v>
+        <v>60</v>
       </c>
       <c r="E97">
-        <v>95.2</v>
+        <v>96.5</v>
       </c>
       <c r="F97">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="G97">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -6081,28 +6081,28 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MLW_WPV1</t>
+          <t>CHD-2026-03_nOPV_NID</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C98">
-        <v>1313</v>
+        <v>391</v>
       </c>
       <c r="D98">
-        <v>59.8</v>
+        <v>60</v>
       </c>
       <c r="E98">
-        <v>94.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="F98">
-        <v>74.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G98">
-        <v>74.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -6111,28 +6111,28 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>CIV-2023-09-01_nOPV</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C99">
-        <v>159</v>
+        <v>227</v>
       </c>
       <c r="D99">
-        <v>59</v>
+        <v>59.6</v>
       </c>
       <c r="E99">
-        <v>92.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="F99">
-        <v>74.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G99">
-        <v>74.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -6141,28 +6141,28 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DRC-sNID-09-2024_nOPV</t>
+          <t>MDG-2023-03-01_bOPV</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>mOPV</t>
         </is>
       </c>
       <c r="C100">
-        <v>23</v>
+        <v>452</v>
       </c>
       <c r="D100">
-        <v>60</v>
+        <v>58.4</v>
       </c>
       <c r="E100">
-        <v>94.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="F100">
-        <v>73.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G100">
-        <v>73.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -6171,28 +6171,28 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ALG-2023-09-01_nOPV</t>
+          <t>MLW_WPV1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C101">
-        <v>53</v>
+        <v>1313</v>
       </c>
       <c r="D101">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="E101">
-        <v>95.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F101">
-        <v>73.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="G101">
-        <v>73.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -6201,28 +6201,28 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BUU-2023-04-01_nOPV</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C102">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D102">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E102">
-        <v>94.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F102">
-        <v>73.5</v>
+        <v>74.2</v>
       </c>
       <c r="G102">
-        <v>73.5</v>
+        <v>74.2</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -6231,7 +6231,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RCA-2025-10-01_nOPV_NIDs</t>
+          <t>ALG-2023-09-01_nOPV</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6240,19 +6240,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D103">
-        <v>61.3</v>
+        <v>60</v>
       </c>
       <c r="E103">
-        <v>94.7</v>
+        <v>95.2</v>
       </c>
       <c r="F103">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G103">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H103">
         <v>0</v>
@@ -6261,7 +6261,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TNZ-2026-02-01_nOPV_sNID</t>
+          <t>BUU-2023-04-01_nOPV</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6270,19 +6270,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="D104">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E104">
-        <v>93.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="F104">
-        <v>73</v>
+        <v>73.5</v>
       </c>
       <c r="G104">
-        <v>73</v>
+        <v>73.5</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -6291,7 +6291,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DRC-NID-03-2024-B_nOPV</t>
+          <t>TNZ-2026-02-01_nOPV_sNID</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6300,19 +6300,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>229</v>
+        <v>100</v>
       </c>
       <c r="D105">
-        <v>57.6</v>
+        <v>59.9</v>
       </c>
       <c r="E105">
-        <v>96.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="F105">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="G105">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -6321,7 +6321,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CAR-2024-sNIDs-11_nOPV</t>
+          <t>NIE-2024-nOPV2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6330,28 +6330,28 @@
         </is>
       </c>
       <c r="C106">
-        <v>22</v>
+        <v>1254</v>
       </c>
       <c r="D106">
-        <v>55.9</v>
+        <v>61.3</v>
       </c>
       <c r="E106">
-        <v>96.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F106">
-        <v>72.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G106">
-        <v>72.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NIE-2024-nOPV2</t>
+          <t>GUI-2026-01-SNID-bOPV_nOPV</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6360,49 +6360,44 @@
         </is>
       </c>
       <c r="C107">
-        <v>1254</v>
+        <v>18</v>
       </c>
       <c r="D107">
-        <v>61.3</v>
+        <v>59.4</v>
       </c>
       <c r="E107">
-        <v>97.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F107">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G107">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="H107">
-        <v>89.90000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DRC-2023-05-01_nOPV</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>nOPV2</t>
+          <t>SSD-2026-01-05_NOPV2</t>
         </is>
       </c>
       <c r="C108">
-        <v>275</v>
+        <v>18</v>
       </c>
       <c r="D108">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E108">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F108">
-        <v>70.5</v>
+        <v>72.2</v>
       </c>
       <c r="G108">
-        <v>70.5</v>
+        <v>72.2</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -6411,28 +6406,28 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MOZ-2023-05-01_bOPV</t>
+          <t>ZIM-2026-03-01_nOPV_sNID</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C109">
-        <v>322</v>
+        <v>90</v>
       </c>
       <c r="D109">
-        <v>60</v>
+        <v>57.9</v>
       </c>
       <c r="E109">
-        <v>91.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F109">
-        <v>70.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G109">
-        <v>70.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -6441,28 +6436,28 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ANG-2026-03-01_nOPV_NID</t>
+          <t>MOZ-2023-05-01_bOPV</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C110">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D110">
-        <v>65.7</v>
+        <v>60</v>
       </c>
       <c r="E110">
-        <v>94.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="F110">
-        <v>70.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="G110">
-        <v>70.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -6513,7 +6508,7 @@
         <v>622</v>
       </c>
       <c r="D112">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="E112">
         <v>94.3</v>
@@ -6711,7 +6706,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CAR-2024-sNIDs-09_nOPV</t>
+          <t>nOPV2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6720,19 +6715,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>9</v>
+        <v>922</v>
       </c>
       <c r="D119">
-        <v>56.7</v>
+        <v>59.6</v>
       </c>
       <c r="E119">
-        <v>96.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F119">
-        <v>66.7</v>
+        <v>66.3</v>
       </c>
       <c r="G119">
-        <v>66.7</v>
+        <v>66.3</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -6741,7 +6736,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>nOPV2022</t>
+          <t>EBOLOWA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6750,19 +6745,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>922</v>
+        <v>20</v>
       </c>
       <c r="D120">
-        <v>59.6</v>
+        <v>60</v>
       </c>
       <c r="E120">
-        <v>93.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="F120">
-        <v>66.3</v>
+        <v>65</v>
       </c>
       <c r="G120">
-        <v>66.3</v>
+        <v>65</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -6771,7 +6766,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EBOLOWA</t>
+          <t>ETH-2025-12-b-nOPV2-NIDs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6780,13 +6775,13 @@
         </is>
       </c>
       <c r="C121">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="D121">
-        <v>60</v>
+        <v>151.3</v>
       </c>
       <c r="E121">
-        <v>92.8</v>
+        <v>97.7</v>
       </c>
       <c r="F121">
         <v>65</v>
@@ -6801,7 +6796,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ETH-2025-12-b-nOPV2-NIDs</t>
+          <t>GHA-2024-10-01_nOPV</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6810,19 +6805,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>143</v>
+        <v>534</v>
       </c>
       <c r="D122">
-        <v>151.3</v>
+        <v>60</v>
       </c>
       <c r="E122">
-        <v>97.7</v>
+        <v>93.7</v>
       </c>
       <c r="F122">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G122">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -6831,22 +6826,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GHA-2024-10-01_nOPV</t>
+          <t>NGA-2021-013-1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C123">
-        <v>534</v>
+        <v>130</v>
       </c>
       <c r="D123">
-        <v>60</v>
+        <v>56.1</v>
       </c>
       <c r="E123">
-        <v>93.7</v>
+        <v>95.5</v>
       </c>
       <c r="F123">
         <v>64.59999999999999</v>
@@ -6855,43 +6850,43 @@
         <v>64.59999999999999</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NGA-2021-013-1</t>
+          <t>AMANSIE SOUTH</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C124">
-        <v>130</v>
+        <v>358</v>
       </c>
       <c r="D124">
-        <v>56.1</v>
+        <v>59.9</v>
       </c>
       <c r="E124">
-        <v>95.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F124">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="G124">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="H124">
-        <v>86.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AMANSIE SOUTH</t>
+          <t>NAM-2025-12-n_OPV-NIDs</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6900,19 +6895,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>358</v>
+        <v>115</v>
       </c>
       <c r="D125">
         <v>59.9</v>
       </c>
       <c r="E125">
-        <v>93.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="F125">
-        <v>64.5</v>
+        <v>64.3</v>
       </c>
       <c r="G125">
-        <v>64.5</v>
+        <v>64.3</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -6921,22 +6916,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NAM-2025-12-n_OPV-NIDs</t>
+          <t>WPV1MLW</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C126">
-        <v>113</v>
+        <v>504</v>
       </c>
       <c r="D126">
-        <v>59.9</v>
+        <v>59.5</v>
       </c>
       <c r="E126">
-        <v>92.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="F126">
         <v>63.7</v>
@@ -6951,28 +6946,28 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>WPV1MLW</t>
+          <t>BOT-2023-02-01_nOPV</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C127">
-        <v>504</v>
+        <v>54</v>
       </c>
       <c r="D127">
-        <v>59.5</v>
+        <v>60</v>
       </c>
       <c r="E127">
-        <v>93.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F127">
-        <v>63.7</v>
+        <v>63</v>
       </c>
       <c r="G127">
-        <v>63.7</v>
+        <v>63</v>
       </c>
       <c r="H127">
         <v>0</v>
@@ -6981,23 +6976,28 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DRC-2025-10-01_n-OPV_sNID</t>
+          <t>CAM-2024-02-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C128">
-        <v>11</v>
+        <v>161</v>
       </c>
       <c r="D128">
-        <v>45.5</v>
+        <v>59.9</v>
       </c>
       <c r="E128">
-        <v>99.5</v>
+        <v>93</v>
       </c>
       <c r="F128">
-        <v>63.6</v>
+        <v>62.7</v>
       </c>
       <c r="G128">
-        <v>63.6</v>
+        <v>62.7</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -7006,7 +7006,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BOT-2023-02-01_nOPV</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7015,19 +7015,19 @@
         </is>
       </c>
       <c r="C129">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D129">
-        <v>60</v>
+        <v>51.2</v>
       </c>
       <c r="E129">
-        <v>89.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="F129">
-        <v>63</v>
+        <v>62.5</v>
       </c>
       <c r="G129">
-        <v>63</v>
+        <v>62.5</v>
       </c>
       <c r="H129">
         <v>0</v>
@@ -7036,7 +7036,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CAM-2024-02-01_nOPV</t>
+          <t>BEN-2023-09-01_nOPV</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7045,19 +7045,19 @@
         </is>
       </c>
       <c r="C130">
-        <v>161</v>
+        <v>45</v>
       </c>
       <c r="D130">
-        <v>59.9</v>
+        <v>57.8</v>
       </c>
       <c r="E130">
-        <v>93</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F130">
-        <v>62.7</v>
+        <v>62.2</v>
       </c>
       <c r="G130">
-        <v>62.7</v>
+        <v>62.2</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -7066,28 +7066,28 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DRC-2023-03-01_bOPV</t>
+          <t>CAM-2023-08-01_nOPV</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C131">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="D131">
-        <v>55.1</v>
+        <v>59.7</v>
       </c>
       <c r="E131">
-        <v>95.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F131">
-        <v>62.7</v>
+        <v>62.1</v>
       </c>
       <c r="G131">
-        <v>62.7</v>
+        <v>62.1</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -7096,7 +7096,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>KEN-2023-08-01_nOPV</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7105,19 +7105,19 @@
         </is>
       </c>
       <c r="C132">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="D132">
-        <v>51.2</v>
+        <v>60</v>
       </c>
       <c r="E132">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="F132">
-        <v>62.5</v>
+        <v>61.6</v>
       </c>
       <c r="G132">
-        <v>62.5</v>
+        <v>61.6</v>
       </c>
       <c r="H132">
         <v>0</v>
@@ -7126,7 +7126,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BEN-2023-09-01_nOPV</t>
+          <t>UGA-2024-08-01_nOPV</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7135,19 +7135,19 @@
         </is>
       </c>
       <c r="C133">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="D133">
-        <v>57.8</v>
+        <v>59.9</v>
       </c>
       <c r="E133">
-        <v>94.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="F133">
-        <v>62.2</v>
+        <v>61.2</v>
       </c>
       <c r="G133">
-        <v>62.2</v>
+        <v>61.2</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -7156,28 +7156,23 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CAM-2023-08-01_nOPV</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>nOPV2</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="C134">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="D134">
-        <v>59.7</v>
+        <v>167</v>
       </c>
       <c r="E134">
-        <v>90.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F134">
-        <v>62.1</v>
+        <v>59.6</v>
       </c>
       <c r="G134">
-        <v>62.1</v>
+        <v>59.6</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -7186,7 +7181,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>KEN-2023-08-01_nOPV</t>
+          <t>KEN-2024-08-01_nOPV</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7195,19 +7190,19 @@
         </is>
       </c>
       <c r="C135">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="D135">
         <v>60</v>
       </c>
       <c r="E135">
-        <v>92.7</v>
+        <v>93.2</v>
       </c>
       <c r="F135">
-        <v>61.6</v>
+        <v>59.2</v>
       </c>
       <c r="G135">
-        <v>61.6</v>
+        <v>59.2</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -7216,28 +7211,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UGA-2024-08-01_nOPV</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>nOPV2</t>
+          <t>DRC-2025-10-01_n-OPV_sNID</t>
         </is>
       </c>
       <c r="C136">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="D136">
-        <v>59.9</v>
+        <v>48.4</v>
       </c>
       <c r="E136">
-        <v>92.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F136">
-        <v>61.2</v>
+        <v>59.1</v>
       </c>
       <c r="G136">
-        <v>61.2</v>
+        <v>59.1</v>
       </c>
       <c r="H136">
         <v>0</v>
@@ -7246,28 +7236,28 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DRC-2023-09-KIN_nOPV</t>
+          <t>ETH-2026-05-bOPV-sNID</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C137">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D137">
-        <v>58.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="E137">
-        <v>94.5</v>
+        <v>96.5</v>
       </c>
       <c r="F137">
-        <v>60</v>
+        <v>59.1</v>
       </c>
       <c r="G137">
-        <v>60</v>
+        <v>59.1</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -7276,23 +7266,28 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>ANGOLA-NID-2024-nOPV2</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C138">
-        <v>267</v>
+        <v>356</v>
       </c>
       <c r="D138">
-        <v>167</v>
+        <v>59.9</v>
       </c>
       <c r="E138">
-        <v>96.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F138">
-        <v>59.6</v>
+        <v>56.7</v>
       </c>
       <c r="G138">
-        <v>59.6</v>
+        <v>56.7</v>
       </c>
       <c r="H138">
         <v>0</v>
@@ -7301,28 +7296,28 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>KEN-2024-08-01_nOPV</t>
+          <t>BEN-26DS-08-2020</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>mOPV</t>
         </is>
       </c>
       <c r="C139">
-        <v>142</v>
+        <v>23</v>
       </c>
       <c r="D139">
-        <v>60</v>
+        <v>58.7</v>
       </c>
       <c r="E139">
-        <v>93.2</v>
+        <v>94.2</v>
       </c>
       <c r="F139">
-        <v>59.2</v>
+        <v>56.5</v>
       </c>
       <c r="G139">
-        <v>59.2</v>
+        <v>56.5</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -7331,7 +7326,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ETH-2026-05-bOPV-sNID</t>
+          <t>ZIM-2023-05-01_bOPV</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7340,19 +7335,19 @@
         </is>
       </c>
       <c r="C140">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D140">
-        <v>83.59999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="E140">
-        <v>96.5</v>
+        <v>93.3</v>
       </c>
       <c r="F140">
-        <v>59.1</v>
+        <v>56.4</v>
       </c>
       <c r="G140">
-        <v>59.1</v>
+        <v>56.4</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -7361,7 +7356,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ANGOLA-NID-2024-nOPV2</t>
+          <t>SLE-2024-05-01_nOPV</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7370,19 +7365,19 @@
         </is>
       </c>
       <c r="C141">
-        <v>356</v>
+        <v>48</v>
       </c>
       <c r="D141">
-        <v>59.9</v>
+        <v>59.4</v>
       </c>
       <c r="E141">
-        <v>91.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="F141">
-        <v>56.7</v>
+        <v>56.2</v>
       </c>
       <c r="G141">
-        <v>56.7</v>
+        <v>56.2</v>
       </c>
       <c r="H141">
         <v>0</v>
@@ -7391,28 +7386,28 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BEN-26DS-08-2020</t>
+          <t>CHD-2024-11-1_nOPV</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>mOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C142">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="D142">
-        <v>58.7</v>
+        <v>60</v>
       </c>
       <c r="E142">
-        <v>94.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F142">
-        <v>56.5</v>
+        <v>56.1</v>
       </c>
       <c r="G142">
-        <v>56.5</v>
+        <v>56.1</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -7421,28 +7416,28 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ZIM-2023-05-01_bOPV</t>
+          <t>CHD-2025-05-1_nOPV_NID</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C143">
-        <v>149</v>
+        <v>356</v>
       </c>
       <c r="D143">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="E143">
-        <v>93.3</v>
+        <v>89.7</v>
       </c>
       <c r="F143">
-        <v>56.4</v>
+        <v>55.6</v>
       </c>
       <c r="G143">
-        <v>56.4</v>
+        <v>55.6</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -7451,28 +7446,28 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SLE-2024-05-01_nOPV</t>
+          <t>Luapula-mOPV</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>mOPV</t>
         </is>
       </c>
       <c r="C144">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D144">
-        <v>59.4</v>
+        <v>57</v>
       </c>
       <c r="E144">
-        <v>91.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F144">
-        <v>56.2</v>
+        <v>55</v>
       </c>
       <c r="G144">
-        <v>56.2</v>
+        <v>55</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -7481,7 +7476,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CHD-2024-11-1_nOPV</t>
+          <t>MLW-2026-02-1_nOPV</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7490,19 +7485,19 @@
         </is>
       </c>
       <c r="C145">
-        <v>157</v>
+        <v>95</v>
       </c>
       <c r="D145">
         <v>60</v>
       </c>
       <c r="E145">
-        <v>88.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="F145">
-        <v>56.1</v>
+        <v>54.7</v>
       </c>
       <c r="G145">
-        <v>56.1</v>
+        <v>54.7</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -7511,7 +7506,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CHD-2025-05-1_nOPV_NID</t>
+          <t>GOLFE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7520,19 +7515,19 @@
         </is>
       </c>
       <c r="C146">
-        <v>356</v>
+        <v>26</v>
       </c>
       <c r="D146">
-        <v>60</v>
+        <v>59.2</v>
       </c>
       <c r="E146">
-        <v>89.7</v>
+        <v>88.2</v>
       </c>
       <c r="F146">
-        <v>55.6</v>
+        <v>53.8</v>
       </c>
       <c r="G146">
-        <v>55.6</v>
+        <v>53.8</v>
       </c>
       <c r="H146">
         <v>0</v>
@@ -7541,28 +7536,28 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Luapula-mOPV</t>
+          <t>OPVb2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>mOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C147">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D147">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E147">
-        <v>96.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="F147">
-        <v>55</v>
+        <v>53.8</v>
       </c>
       <c r="G147">
-        <v>55</v>
+        <v>53.8</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -7571,7 +7566,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tanganyika</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7580,19 +7575,19 @@
         </is>
       </c>
       <c r="C148">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D148">
-        <v>57.3</v>
+        <v>60</v>
       </c>
       <c r="E148">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="F148">
-        <v>54.5</v>
+        <v>53.6</v>
       </c>
       <c r="G148">
-        <v>54.5</v>
+        <v>53.6</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -7601,7 +7596,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ZIM-2026-03-01_nOPV_sNID</t>
+          <t>ANGOLA-SNID-2024-07-nOPV2</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7610,19 +7605,19 @@
         </is>
       </c>
       <c r="C149">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="D149">
-        <v>54.2</v>
+        <v>59.9</v>
       </c>
       <c r="E149">
-        <v>94.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F149">
-        <v>54.5</v>
+        <v>53.4</v>
       </c>
       <c r="G149">
-        <v>54.5</v>
+        <v>53.4</v>
       </c>
       <c r="H149">
         <v>0</v>
@@ -7631,7 +7626,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GOLFE</t>
+          <t>OPVb2021</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7640,19 +7635,19 @@
         </is>
       </c>
       <c r="C150">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D150">
-        <v>59.2</v>
+        <v>59.7</v>
       </c>
       <c r="E150">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="F150">
-        <v>53.8</v>
+        <v>53.3</v>
       </c>
       <c r="G150">
-        <v>53.8</v>
+        <v>53.3</v>
       </c>
       <c r="H150">
         <v>0</v>
@@ -7661,7 +7656,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>OPVb2022</t>
+          <t>SEN_VPOn</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7670,19 +7665,19 @@
         </is>
       </c>
       <c r="C151">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="D151">
-        <v>60</v>
+        <v>59.7</v>
       </c>
       <c r="E151">
-        <v>89.3</v>
+        <v>90.3</v>
       </c>
       <c r="F151">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
       <c r="G151">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -7691,7 +7686,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>CENBLOCK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7700,19 +7695,19 @@
         </is>
       </c>
       <c r="C152">
-        <v>28</v>
+        <v>379</v>
       </c>
       <c r="D152">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="E152">
-        <v>90.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F152">
-        <v>53.6</v>
+        <v>52.5</v>
       </c>
       <c r="G152">
-        <v>53.6</v>
+        <v>52.5</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -7721,37 +7716,37 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ANGOLA-SNID-2024-07-nOPV2</t>
+          <t>NGA-2021-011-1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C153">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D153">
-        <v>59.9</v>
+        <v>56</v>
       </c>
       <c r="E153">
-        <v>91.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="F153">
-        <v>53.4</v>
+        <v>52.5</v>
       </c>
       <c r="G153">
-        <v>53.4</v>
+        <v>52.5</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OPVb2021</t>
+          <t>KEN-13DS-02-2021</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7760,19 +7755,19 @@
         </is>
       </c>
       <c r="C154">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="D154">
-        <v>59.7</v>
+        <v>60</v>
       </c>
       <c r="E154">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="F154">
-        <v>53.3</v>
+        <v>52.2</v>
       </c>
       <c r="G154">
-        <v>53.3</v>
+        <v>52.2</v>
       </c>
       <c r="H154">
         <v>0</v>
@@ -7781,7 +7776,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SEN_VPOn</t>
+          <t>SSD-2024-10-01_nOPV2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7790,19 +7785,19 @@
         </is>
       </c>
       <c r="C155">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="D155">
-        <v>59.7</v>
+        <v>60.1</v>
       </c>
       <c r="E155">
-        <v>90.3</v>
+        <v>90</v>
       </c>
       <c r="F155">
-        <v>53.2</v>
+        <v>51.9</v>
       </c>
       <c r="G155">
-        <v>53.2</v>
+        <v>51.9</v>
       </c>
       <c r="H155">
         <v>0</v>
@@ -7811,7 +7806,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CENBLOCK</t>
+          <t>BERTOUA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7820,19 +7815,19 @@
         </is>
       </c>
       <c r="C156">
-        <v>379</v>
+        <v>232</v>
       </c>
       <c r="D156">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
       <c r="E156">
-        <v>89.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="F156">
-        <v>52.5</v>
+        <v>51.3</v>
       </c>
       <c r="G156">
-        <v>52.5</v>
+        <v>51.3</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -7841,7 +7836,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NGA-2021-011-1</t>
+          <t>CAM-2025-08-01_bOPV_sNID</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7850,49 +7845,49 @@
         </is>
       </c>
       <c r="C157">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D157">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E157">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="F157">
-        <v>52.5</v>
+        <v>50</v>
       </c>
       <c r="G157">
-        <v>52.5</v>
+        <v>50</v>
       </c>
       <c r="H157">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>KEN-13DS-02-2021</t>
+          <t>CONAKRY-mOPV</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>mOPV</t>
         </is>
       </c>
       <c r="C158">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="D158">
-        <v>60</v>
+        <v>59.5</v>
       </c>
       <c r="E158">
-        <v>91.3</v>
+        <v>87.3</v>
       </c>
       <c r="F158">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="G158">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="H158">
         <v>0</v>
@@ -7901,7 +7896,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SSD-2024-10-01_nOPV2</t>
+          <t>VPOb</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7910,19 +7905,19 @@
         </is>
       </c>
       <c r="C159">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="D159">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="E159">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="F159">
-        <v>51.9</v>
+        <v>50</v>
       </c>
       <c r="G159">
-        <v>51.9</v>
+        <v>50</v>
       </c>
       <c r="H159">
         <v>0</v>
@@ -7931,7 +7926,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BERTOUA</t>
+          <t>RSSmOPV10C2021</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7940,19 +7935,21 @@
         </is>
       </c>
       <c r="C160">
-        <v>232</v>
+        <v>53</v>
       </c>
       <c r="D160">
-        <v>59.9</v>
-      </c>
-      <c r="E160">
-        <v>90.3</v>
+        <v>58.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="F160">
-        <v>51.3</v>
+        <v>49.1</v>
       </c>
       <c r="G160">
-        <v>51.3</v>
+        <v>49.1</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -7961,28 +7958,28 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CAM-2025-08-01_bOPV_sNID</t>
+          <t>MOZ-2025-10-1_nOPV_sNID</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C161">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="D161">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="E161">
-        <v>91.7</v>
+        <v>83.8</v>
       </c>
       <c r="F161">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="G161">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -7991,28 +7988,28 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CONAKRY-mOPV</t>
+          <t>MAU_57DS_08-2021nOPV</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>mOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C162">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="D162">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="E162">
-        <v>87.3</v>
+        <v>81</v>
       </c>
       <c r="F162">
-        <v>50</v>
+        <v>45.4</v>
       </c>
       <c r="G162">
-        <v>50</v>
+        <v>45.4</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -8021,7 +8018,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>VPOb</t>
+          <t>BOT-2026-02-1_nOPV_NID</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8030,19 +8027,19 @@
         </is>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D163">
-        <v>60</v>
+        <v>59.2</v>
       </c>
       <c r="E163">
-        <v>93.3</v>
+        <v>89.3</v>
       </c>
       <c r="F163">
-        <v>50</v>
+        <v>45.2</v>
       </c>
       <c r="G163">
-        <v>50</v>
+        <v>45.2</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -8051,30 +8048,28 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RSSmOPV10C2021</t>
+          <t>WPV1Response</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C164">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="D164">
-        <v>58.1</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="E164">
+        <v>88.09999999999999</v>
       </c>
       <c r="F164">
-        <v>49.1</v>
+        <v>43.1</v>
       </c>
       <c r="G164">
-        <v>49.1</v>
+        <v>43.1</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -8083,28 +8078,28 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DRC-2025-11-01_n-bOPV_NID</t>
+          <t>ADDIS ABABA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C165">
-        <v>367</v>
+        <v>86</v>
       </c>
       <c r="D165">
-        <v>48.9</v>
+        <v>203.7</v>
       </c>
       <c r="E165">
-        <v>97.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F165">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G165">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -8113,7 +8108,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MLW-2026-02-1_nOPV</t>
+          <t>SSD-2024-02-01_nOPV2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8122,19 +8117,19 @@
         </is>
       </c>
       <c r="C166">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D166">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="E166">
-        <v>91.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F166">
-        <v>45.5</v>
+        <v>43</v>
       </c>
       <c r="G166">
-        <v>45.5</v>
+        <v>43</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -8143,28 +8138,23 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MAU_57DS_08-2021nOPV</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>nOPV2</t>
+          <t>NID_LID_preventive</t>
         </is>
       </c>
       <c r="C167">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="D167">
-        <v>59.4</v>
+        <v>60</v>
       </c>
       <c r="E167">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F167">
-        <v>45.4</v>
+        <v>41.8</v>
       </c>
       <c r="G167">
-        <v>45.4</v>
+        <v>41.8</v>
       </c>
       <c r="H167">
         <v>0</v>
@@ -8173,28 +8163,28 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>WPV1Response</t>
+          <t>SSD-79DS-09-2020</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C168">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="D168">
-        <v>60</v>
+        <v>59.7</v>
       </c>
       <c r="E168">
-        <v>88.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F168">
-        <v>43.1</v>
+        <v>40.6</v>
       </c>
       <c r="G168">
-        <v>43.1</v>
+        <v>40.6</v>
       </c>
       <c r="H168">
         <v>0</v>
@@ -8203,7 +8193,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ADDIS ABABA</t>
+          <t>RSS-2025-08-01_nOPV-sNID</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8212,19 +8202,19 @@
         </is>
       </c>
       <c r="C169">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D169">
-        <v>203.7</v>
+        <v>58</v>
       </c>
       <c r="E169">
-        <v>94.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F169">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G169">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H169">
         <v>0</v>
@@ -8233,7 +8223,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SSD-2024-02-01_nOPV2</t>
+          <t>SSD-2026-01-05_nOPV2</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8242,19 +8232,19 @@
         </is>
       </c>
       <c r="C170">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="D170">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="E170">
-        <v>88.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F170">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G170">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H170">
         <v>0</v>
@@ -8263,23 +8253,28 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NID_LID_preventive</t>
+          <t>UGAnOPV</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C171">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="D171">
         <v>60</v>
       </c>
       <c r="E171">
-        <v>84</v>
+        <v>86.7</v>
       </c>
       <c r="F171">
-        <v>41.8</v>
+        <v>39.6</v>
       </c>
       <c r="G171">
-        <v>41.8</v>
+        <v>39.6</v>
       </c>
       <c r="H171">
         <v>0</v>
@@ -8288,28 +8283,28 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SSD-79DS-09-2020</t>
+          <t>KANKAN-mOPV</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>mOPV</t>
         </is>
       </c>
       <c r="C172">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D172">
         <v>59.7</v>
       </c>
       <c r="E172">
-        <v>90.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F172">
-        <v>40.6</v>
+        <v>38.9</v>
       </c>
       <c r="G172">
-        <v>40.6</v>
+        <v>38.9</v>
       </c>
       <c r="H172">
         <v>0</v>
@@ -8318,7 +8313,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BOT-2026-02-1_nOPV_NID</t>
+          <t>GUI-2023-09-01_nOPV</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8327,19 +8322,19 @@
         </is>
       </c>
       <c r="C173">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="D173">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="E173">
-        <v>87.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="F173">
-        <v>40</v>
+        <v>38.3</v>
       </c>
       <c r="G173">
-        <v>40</v>
+        <v>38.3</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -8348,28 +8343,28 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>RSS-2025-08-01_nOPV-sNID</t>
+          <t>CNG-2023-05-bOPV</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C174">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="D174">
-        <v>58</v>
+        <v>58.8</v>
       </c>
       <c r="E174">
-        <v>91.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F174">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="G174">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="H174">
         <v>0</v>
@@ -8378,7 +8373,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>UGAnOPV</t>
+          <t>MAU-2024-01-01_nOPV</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -8387,19 +8382,19 @@
         </is>
       </c>
       <c r="C175">
-        <v>230</v>
+        <v>124</v>
       </c>
       <c r="D175">
         <v>60</v>
       </c>
       <c r="E175">
-        <v>86.7</v>
+        <v>82</v>
       </c>
       <c r="F175">
-        <v>39.6</v>
+        <v>34.7</v>
       </c>
       <c r="G175">
-        <v>39.6</v>
+        <v>34.7</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -8408,28 +8403,28 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KANKAN-mOPV</t>
+          <t>nVPO</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>mOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C176">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D176">
-        <v>59.7</v>
+        <v>59.3</v>
       </c>
       <c r="E176">
-        <v>86.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="F176">
-        <v>38.9</v>
+        <v>31.7</v>
       </c>
       <c r="G176">
-        <v>38.9</v>
+        <v>31.7</v>
       </c>
       <c r="H176">
         <v>0</v>
@@ -8438,7 +8433,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GUI-2023-09-01_nOPV</t>
+          <t>BEN-39DS-01-2021</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8447,19 +8442,19 @@
         </is>
       </c>
       <c r="C177">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="D177">
-        <v>59.9</v>
+        <v>58.9</v>
       </c>
       <c r="E177">
-        <v>88.2</v>
+        <v>86.8</v>
       </c>
       <c r="F177">
-        <v>38.3</v>
+        <v>29.5</v>
       </c>
       <c r="G177">
-        <v>38.3</v>
+        <v>29.5</v>
       </c>
       <c r="H177">
         <v>0</v>
@@ -8468,7 +8463,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CNG-2023-05-bOPV</t>
+          <t>ANG-2023-07-01_bOPV</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8477,19 +8472,19 @@
         </is>
       </c>
       <c r="C178">
-        <v>104</v>
+        <v>332</v>
       </c>
       <c r="D178">
-        <v>58.8</v>
+        <v>59.1</v>
       </c>
       <c r="E178">
-        <v>86.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F178">
-        <v>37.5</v>
+        <v>23.2</v>
       </c>
       <c r="G178">
-        <v>37.5</v>
+        <v>23.2</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -8498,28 +8493,28 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MAU-2024-01-01_nOPV</t>
+          <t>DRC-2026-03-NID_bOPV-Nopv</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C179">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="D179">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E179">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F179">
-        <v>34.7</v>
+        <v>0</v>
       </c>
       <c r="G179">
-        <v>34.7</v>
+        <v>0</v>
       </c>
       <c r="H179">
         <v>0</v>
@@ -8528,7 +8523,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MOZ-2025-10-1_nOPV_sNID</t>
+          <t>Mekelle</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8537,19 +8532,19 @@
         </is>
       </c>
       <c r="C180">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D180">
-        <v>38.3</v>
+        <v>381.7</v>
       </c>
       <c r="E180">
-        <v>88.3</v>
+        <v>68.7</v>
       </c>
       <c r="F180">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G180">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H180">
         <v>0</v>
@@ -8558,7 +8553,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>nVPO</t>
+          <t>SSD-2024-02-01_nOPV</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8567,231 +8562,21 @@
         </is>
       </c>
       <c r="C181">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D181">
-        <v>59.3</v>
+        <v>60</v>
       </c>
       <c r="E181">
-        <v>83.2</v>
+        <v>72.5</v>
       </c>
       <c r="F181">
-        <v>31.7</v>
+        <v>0</v>
       </c>
       <c r="G181">
-        <v>31.7</v>
+        <v>0</v>
       </c>
       <c r="H181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>BEN-39DS-01-2021</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>nOPV2</t>
-        </is>
-      </c>
-      <c r="C182">
-        <v>122</v>
-      </c>
-      <c r="D182">
-        <v>59</v>
-      </c>
-      <c r="E182">
-        <v>86.8</v>
-      </c>
-      <c r="F182">
-        <v>29.5</v>
-      </c>
-      <c r="G182">
-        <v>29.5</v>
-      </c>
-      <c r="H182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>DRC-2025-11-01_n-BOPV_sNID</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>bOPV</t>
-        </is>
-      </c>
-      <c r="C183">
-        <v>188</v>
-      </c>
-      <c r="D183">
-        <v>41.8</v>
-      </c>
-      <c r="E183">
-        <v>98.8</v>
-      </c>
-      <c r="F183">
-        <v>25</v>
-      </c>
-      <c r="G183">
-        <v>25</v>
-      </c>
-      <c r="H183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>ANG-2023-07-01_bOPV</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>bOPV</t>
-        </is>
-      </c>
-      <c r="C184">
-        <v>332</v>
-      </c>
-      <c r="D184">
-        <v>59.1</v>
-      </c>
-      <c r="E184">
-        <v>72.5</v>
-      </c>
-      <c r="F184">
-        <v>23.2</v>
-      </c>
-      <c r="G184">
-        <v>23.2</v>
-      </c>
-      <c r="H184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Mekelle</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>nOPV2</t>
-        </is>
-      </c>
-      <c r="C185">
-        <v>12</v>
-      </c>
-      <c r="D185">
-        <v>381.7</v>
-      </c>
-      <c r="E185">
-        <v>68.7</v>
-      </c>
-      <c r="F185">
-        <v>0</v>
-      </c>
-      <c r="G185">
-        <v>0</v>
-      </c>
-      <c r="H185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>RCA-2026-03_nOPV_NIDs</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>nOPV2</t>
-        </is>
-      </c>
-      <c r="C186">
-        <v>1</v>
-      </c>
-      <c r="D186">
-        <v>20</v>
-      </c>
-      <c r="E186">
-        <v>100</v>
-      </c>
-      <c r="F186">
-        <v>0</v>
-      </c>
-      <c r="G186">
-        <v>0</v>
-      </c>
-      <c r="H186">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>SSD-2024-02-01_nOPV</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>nOPV2</t>
-        </is>
-      </c>
-      <c r="C187">
-        <v>2</v>
-      </c>
-      <c r="D187">
-        <v>60</v>
-      </c>
-      <c r="E187">
-        <v>72.5</v>
-      </c>
-      <c r="F187">
-        <v>0</v>
-      </c>
-      <c r="G187">
-        <v>0</v>
-      </c>
-      <c r="H187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>SSD-2026-01-05_nOPV2</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>nOPV2</t>
-        </is>
-      </c>
-      <c r="C188">
-        <v>3</v>
-      </c>
-      <c r="D188">
-        <v>40</v>
-      </c>
-      <c r="E188">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="F188">
-        <v>0</v>
-      </c>
-      <c r="G188">
-        <v>0</v>
-      </c>
-      <c r="H188">
         <v>0</v>
       </c>
     </row>
@@ -8837,7 +8622,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-17 10:04:19</t>
+          <t>2026-08-15 16:32:42</t>
         </is>
       </c>
     </row>

--- a/data/metadata/lqas_metadata.xlsx
+++ b/data/metadata/lqas_metadata.xlsx
@@ -423,7 +423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-15 16:32:42</t>
+          <t>2026-08-17 11:24:05</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-15 16:32:42</t>
+          <t>2026-08-17 11:24:05</t>
         </is>
       </c>
     </row>

--- a/data/metadata/lqas_metadata.xlsx
+++ b/data/metadata/lqas_metadata.xlsx
@@ -423,7 +423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-17 11:24:05</t>
+          <t>2026-08-18 12:54:05</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17 11:24:05</t>
+          <t>2026-08-18 12:54:05</t>
         </is>
       </c>
     </row>

--- a/data/metadata/lqas_metadata.xlsx
+++ b/data/metadata/lqas_metadata.xlsx
@@ -423,7 +423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-18 12:54:05</t>
+          <t>2026-08-25 13:54:24</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-18 12:54:05</t>
+          <t>2026-08-25 13:54:24</t>
         </is>
       </c>
     </row>

--- a/data/metadata/lqas_metadata.xlsx
+++ b/data/metadata/lqas_metadata.xlsx
@@ -423,7 +423,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 16:22:45</t>
+          <t>2026-09-02 00:20:16</t>
         </is>
       </c>
     </row>
@@ -435,7 +435,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>31928</t>
         </is>
       </c>
     </row>
@@ -447,7 +447,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>5.81</t>
         </is>
       </c>
     </row>
@@ -540,34 +540,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADAMAWA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEMSA</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>ANG-2023-07-01_bOPV</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rnd5</t>
+          <t>Rnd1</t>
         </is>
       </c>
       <c r="F2">
         <v>60</v>
       </c>
       <c r="G2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -576,83 +576,83 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>very poor</t>
         </is>
       </c>
       <c r="J2">
-        <v>98.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADAMAWA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FUFORE</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>ANG-2023-07-01_bOPV</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rnd5</t>
+          <t>Rnd2</t>
         </is>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J3">
-        <v>98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADAMAWA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GANYE</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>ANG-2025-08-01_nOPV-NID</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rnd5</t>
+          <t>Rnd1</t>
         </is>
       </c>
       <c r="F4">
@@ -672,40 +672,40 @@
         </is>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADAMAWA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GIREI</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>ANG-2025-08-01_nOPV-NID</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rnd5</t>
+          <t>Rnd2</t>
         </is>
       </c>
       <c r="F5">
         <v>60</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -718,40 +718,40 @@
         </is>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADAMAWA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GOMBI</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>ANG-2026-03-01_nOPV_NID</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rnd5</t>
+          <t>Rnd1</t>
         </is>
       </c>
       <c r="F6">
         <v>60</v>
       </c>
       <c r="G6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -764,40 +764,40 @@
         </is>
       </c>
       <c r="J6">
-        <v>98.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADAMAWA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GUYUK</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>ANG-2026-03-01_nOPV_NID</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rnd5</t>
+          <t>Rnd2</t>
         </is>
       </c>
       <c r="F7">
         <v>60</v>
       </c>
       <c r="G7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="J7">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ADAMAWA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HONG</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>ANG-2026-08-02_nOPV_NID</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rnd5</t>
+          <t>Rnd1</t>
         </is>
       </c>
       <c r="F8">
@@ -856,33 +856,33 @@
         </is>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADAMAWA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JADA</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>ANGOLA-NID-2024-nOPV2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rnd5</t>
+          <t>Rnd1</t>
         </is>
       </c>
       <c r="F9">
@@ -902,40 +902,40 @@
         </is>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADAMAWA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAMURDE</t>
+          <t>AMBRIZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>ANGOLA-NID-2024-nOPV2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rnd5</t>
+          <t>Rnd2</t>
         </is>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -944,57 +944,57 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>very poor</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="J10">
-        <v>57.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ADAMAWA</t>
+          <t>BENGO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MADAGALI</t>
+          <t>BARRA DO DANDE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>ANG-2025-08-01_nOPV-NID</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rnd5</t>
+          <t>Rnd1</t>
         </is>
       </c>
       <c r="F11">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G11">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1004,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -1056,29 +1056,955 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>325</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2">
+        <v>44908</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="F2">
+        <v>96.5</v>
+      </c>
+      <c r="G2">
+        <v>82.7</v>
+      </c>
+      <c r="H2">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ANG</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>355</v>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2">
+        <v>45186</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46260</v>
+      </c>
+      <c r="F3">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="G3">
+        <v>64.8</v>
+      </c>
+      <c r="H3">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>101</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2">
+        <v>43893</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46190</v>
+      </c>
+      <c r="F4">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G4">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="H4">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BFA</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>71</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2">
+        <v>43924</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46008</v>
+      </c>
+      <c r="F5">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="G5">
+        <v>93.3</v>
+      </c>
+      <c r="H5">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BUI</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>49</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>45091</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F6">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G6">
+        <v>73.5</v>
+      </c>
+      <c r="H6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BWA</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>58</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>44984</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46186</v>
+      </c>
+      <c r="F7">
+        <v>89.2</v>
+      </c>
+      <c r="G7">
+        <v>53.4</v>
+      </c>
+      <c r="H7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>206</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2">
+        <v>44084</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46217</v>
+      </c>
+      <c r="F8">
+        <v>92.5</v>
+      </c>
+      <c r="G8">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="H8">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHD</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>203</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2">
+        <v>43867</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46183</v>
+      </c>
+      <c r="F9">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="G9">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="H9">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>125</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2">
+        <v>44093</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45812</v>
+      </c>
+      <c r="F10">
+        <v>95.7</v>
+      </c>
+      <c r="G10">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="H10">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>COG</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>52</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2">
+        <v>44348</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45567</v>
+      </c>
+      <c r="F11">
+        <v>88.3</v>
+      </c>
+      <c r="G11">
+        <v>51.8</v>
+      </c>
+      <c r="H11">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>211</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2">
+        <v>44490</v>
+      </c>
+      <c r="E12" s="2">
+        <v>46201</v>
+      </c>
+      <c r="F12">
+        <v>96.3</v>
+      </c>
+      <c r="G12">
+        <v>61.4</v>
+      </c>
+      <c r="H12">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GHA</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>261</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>44087</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45811</v>
+      </c>
+      <c r="F13">
+        <v>93.3</v>
+      </c>
+      <c r="G13">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H13">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GNB</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>44682</v>
+      </c>
+      <c r="E14" s="2">
+        <v>44740</v>
+      </c>
+      <c r="F14">
+        <v>96</v>
+      </c>
+      <c r="G14">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H14">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>38</v>
+      </c>
+      <c r="C15">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2">
+        <v>44053</v>
+      </c>
+      <c r="E15" s="2">
+        <v>46197</v>
+      </c>
+      <c r="F15">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G15">
+        <v>67</v>
+      </c>
+      <c r="H15">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KEN</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>143</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2">
+        <v>44342</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45763</v>
+      </c>
+      <c r="F16">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="G16">
+        <v>64.5</v>
+      </c>
+      <c r="H16">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LIB</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>98</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>44288</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45567</v>
+      </c>
+      <c r="F17">
+        <v>95.3</v>
+      </c>
+      <c r="G17">
+        <v>74.3</v>
+      </c>
+      <c r="H17">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MAU</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>70</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>44547</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45440</v>
+      </c>
+      <c r="F18">
+        <v>81.5</v>
+      </c>
+      <c r="G18">
+        <v>40.2</v>
+      </c>
+      <c r="H18">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MDG</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>114</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2">
+        <v>44234</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45487</v>
+      </c>
+      <c r="F19">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="G19">
+        <v>76</v>
+      </c>
+      <c r="H19">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MLW</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>29</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2">
+        <v>44565</v>
+      </c>
+      <c r="E20" s="2">
+        <v>46253</v>
+      </c>
+      <c r="F20">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G20">
+        <v>57.4</v>
+      </c>
+      <c r="H20">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MOZ</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>172</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21" s="2">
+        <v>44565</v>
+      </c>
+      <c r="E21" s="2">
+        <v>46232</v>
+      </c>
+      <c r="F21">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="G21">
+        <v>68</v>
+      </c>
+      <c r="H21">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NAM</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>36</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>46010</v>
+      </c>
+      <c r="E22" s="2">
+        <v>46186</v>
+      </c>
+      <c r="F22">
+        <v>93</v>
+      </c>
+      <c r="G22">
+        <v>64.3</v>
+      </c>
+      <c r="H22">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>NIE</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B23">
         <v>1102</v>
       </c>
-      <c r="C2">
+      <c r="C23">
         <v>10</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D23" s="2">
         <v>43845</v>
       </c>
-      <c r="E2" s="2">
-        <v>46242</v>
-      </c>
-      <c r="F2">
+      <c r="E23" s="2">
+        <v>46261</v>
+      </c>
+      <c r="F23">
         <v>97.09999999999999</v>
       </c>
-      <c r="G2">
+      <c r="G23">
         <v>79.3</v>
       </c>
-      <c r="H2">
-        <v>7977</v>
+      <c r="H23">
+        <v>7978</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NIG</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>77</v>
+      </c>
+      <c r="C24">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2">
+        <v>44101</v>
+      </c>
+      <c r="E24" s="2">
+        <v>46217</v>
+      </c>
+      <c r="F24">
+        <v>96.8</v>
+      </c>
+      <c r="G24">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="H24">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RCA</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>35</v>
+      </c>
+      <c r="C25">
+        <v>11</v>
+      </c>
+      <c r="D25" s="2">
+        <v>44055</v>
+      </c>
+      <c r="E25" s="2">
+        <v>46231</v>
+      </c>
+      <c r="F25">
+        <v>95.7</v>
+      </c>
+      <c r="G25">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="H25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RDC</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>507</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2">
+        <v>45635</v>
+      </c>
+      <c r="E26" s="2">
+        <v>46298</v>
+      </c>
+      <c r="F26">
+        <v>97.8</v>
+      </c>
+      <c r="G26">
+        <v>87</v>
+      </c>
+      <c r="H26">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RWA</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>30</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>45135</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45185</v>
+      </c>
+      <c r="F27">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="G27">
+        <v>80</v>
+      </c>
+      <c r="H27">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>79</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>44552</v>
+      </c>
+      <c r="E28" s="2">
+        <v>44789</v>
+      </c>
+      <c r="F28">
+        <v>90.3</v>
+      </c>
+      <c r="G28">
+        <v>53.2</v>
+      </c>
+      <c r="H28">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SIL</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>16</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2">
+        <v>44349</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45567</v>
+      </c>
+      <c r="F29">
+        <v>91</v>
+      </c>
+      <c r="G29">
+        <v>55.3</v>
+      </c>
+      <c r="H29">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SSUD</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>77</v>
+      </c>
+      <c r="C30">
+        <v>7</v>
+      </c>
+      <c r="D30" s="2">
+        <v>44149</v>
+      </c>
+      <c r="E30" s="2">
+        <v>46219</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>46.9</v>
+      </c>
+      <c r="H30">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TNZ</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>195</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" s="2">
+        <v>44650</v>
+      </c>
+      <c r="E31" s="2">
+        <v>46154</v>
+      </c>
+      <c r="F31">
+        <v>97.2</v>
+      </c>
+      <c r="G31">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="H31">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TOGO</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>44</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+      <c r="D32" s="2">
+        <v>43892</v>
+      </c>
+      <c r="E32" s="2">
+        <v>46133</v>
+      </c>
+      <c r="F32">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="G32">
+        <v>83</v>
+      </c>
+      <c r="H32">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>183</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2">
+        <v>44573</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45610</v>
+      </c>
+      <c r="F33">
+        <v>88.5</v>
+      </c>
+      <c r="G33">
+        <v>46</v>
+      </c>
+      <c r="H33">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ZIM</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>77</v>
+      </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34" s="2">
+        <v>44860</v>
+      </c>
+      <c r="E34" s="2">
+        <v>46215</v>
+      </c>
+      <c r="F34">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G34">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="H34">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ZMB</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>119</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2">
+        <v>43834</v>
+      </c>
+      <c r="E35" s="2">
+        <v>46229</v>
+      </c>
+      <c r="F35">
+        <v>96.5</v>
+      </c>
+      <c r="G35">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="H35">
+        <v>1024</v>
       </c>
     </row>
   </sheetData>
@@ -1088,7 +2014,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1136,7 +2062,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG, GUI, NAM</t>
         </is>
       </c>
     </row>
@@ -1291,19 +2217,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>male_sampled</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>numeric</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Number of male children sampled</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>male_sampled</t>
+          <t>female_sampled</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1313,14 +2244,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Number of male children sampled</t>
+          <t>Number of female children sampled</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>female_sampled</t>
+          <t>total_sampled</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1330,14 +2261,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Number of female children sampled</t>
+          <t>Total number of children sampled (target is 60 per district)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ideal target is 60 children per district</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>total_sampled</t>
+          <t>male_vaccinated</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1347,19 +2283,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Total number of children sampled (target is 60 per district)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Ideal target is 60 children per district</t>
+          <t>Number of male children vaccinated</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>male_vaccinated</t>
+          <t>female_vaccinated</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1369,31 +2300,31 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Number of male children vaccinated</t>
+          <t>Number of female children vaccinated</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>female_vaccinated</t>
+          <t>total_vaccinated</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Number of female children vaccinated</t>
+          <t>Total number of children vaccinated</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>total_vaccinated</t>
+          <t>total_missed</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1403,38 +2334,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Total number of children vaccinated</t>
+          <t>Number of children missed (adjusted for under-sampling)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>If total_sampled &lt; 60: (60 - total_sampled) + missed_child else missed_child</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>missed_child</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>character</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LQAS pass/fail status (Pass if total_missed &lt;= 3)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fail, Pass</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>r_non_compliance</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>character</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Performance classification (high/moderate/poor/very poor)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>very poor, high, moderate</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>r_house_not_visited</t>
+          <t>r_non_compliance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1446,7 +2402,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>r_childabsent</t>
+          <t>r_house_not_visited</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1458,7 +2414,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>r_security</t>
+          <t>r_childabsent</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1470,7 +2426,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>r_childnotborn</t>
+          <t>r_Child_was_asleep</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1482,7 +2438,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>care_giver_informed_sia</t>
+          <t>r_Child_is_a_visitor</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1494,207 +2450,553 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>percent_care_giver_informed_sia</t>
+          <t>r_Vaccinated_but_not_FM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>numeric</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Percentage of caregivers informed about the SIAs</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>total_missed</t>
+          <t>other_r</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>numeric</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Number of children missed (adjusted for under-sampling)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>If total_sampled &lt; 60: (60 - total_sampled) + missed_child else missed_child</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>percent_care_giver_informed_sia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LQAS pass/fail status (Pass if total_missed &lt;= 3)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Fail, Pass</t>
+          <t>Percentage of caregivers informed about the SIAs</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance</t>
+          <t>abs_reason_other</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>character</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Performance classification (high/moderate/poor/very poor)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>moderate, poor, high</t>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Count of children with specific absenteeism reason</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_r</t>
+          <t>abs_reason_travelled</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Count of children with specific absenteeism reason</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>other_r</t>
+          <t>abs_reason_farm</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Count of children with specific absenteeism reason</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>prct_r_non_compliance</t>
+          <t>abs_reason_market</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+          <t>Count of children with specific absenteeism reason</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>prct_r_house_not_visited</t>
+          <t>abs_reason_school</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+          <t>Count of children with specific absenteeism reason</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>prct_r_childabsent</t>
+          <t>abs_reason_in_playground</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+          <t>Count of children with specific absenteeism reason</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>prct_r_childnotborn</t>
+          <t>nc_reason_no_felt_need</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+          <t>Count of children with specific non-compliance reason</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>prct_r_security</t>
+          <t>nc_reason_others</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+          <t>Count of children with specific non-compliance reason</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>nc_reason_child_sick</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Count of children with specific non-compliance reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>nc_reason_vaccines_safety</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Count of children with specific non-compliance reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>nc_reason_religious_cultural</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Count of children with specific non-compliance reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>nc_reason_no_care_giver_consent</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Count of children with specific non-compliance reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>nc_reason_poliofree</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Count of children with specific non-compliance reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>nc_reason_too_many_rnd</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Count of children with specific non-compliance reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>prct_r_non_compliance</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>prct_r_house_not_visited</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>prct_r_childabsent</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>prct_r_Child_was_asleep</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>prct_r_Child_is_a_visitor</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>prct_r_Vaccinated_but_not_FM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>prct_other_r</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>proportion_missed_child</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Proportion of missed children relative to total sampled</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>nc_reason_covid_19</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Count of children with specific non-compliance reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>nc_reason_nopvconcern</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Count of children with specific non-compliance reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>missed_child</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>r_security</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>r_childnotborn</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>care_giver_informed_sia</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>tot_r</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>prct_r_childnotborn</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>prct_r_security</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>Percentage of missed children by specific reason (only calculated when total_missed &gt; 0)</t>
         </is>
@@ -1730,7 +3032,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>31928</t>
         </is>
       </c>
     </row>
@@ -1778,7 +3080,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>723</t>
         </is>
       </c>
     </row>
@@ -1790,7 +3092,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>30837</t>
         </is>
       </c>
     </row>
@@ -1814,7 +3116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>17.38</t>
         </is>
       </c>
     </row>
@@ -1826,7 +3128,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2020-01-04</t>
         </is>
       </c>
     </row>
@@ -1838,7 +3140,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1850,7 +3152,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2464</t>
         </is>
       </c>
     </row>
@@ -1861,7 +3163,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1909,7 +3211,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NIE-2025-04-01_nOPV_NIDs</t>
+          <t>BFA-2023-09-01_nOPV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1918,28 +3220,28 @@
         </is>
       </c>
       <c r="C2">
-        <v>1030</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="E2">
         <v>97.8</v>
       </c>
       <c r="F2">
-        <v>90.2</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>90.2</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIE-2023-07-03_nOPV</t>
+          <t>BFA-2024-08-sNID_nOPV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1948,88 +3250,88 @@
         </is>
       </c>
       <c r="C3">
-        <v>728</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>59.4</v>
+        <v>60</v>
       </c>
       <c r="E3">
-        <v>97.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F3">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>87.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>BITTOU-mOPV2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>mOPV</t>
         </is>
       </c>
       <c r="C4">
-        <v>796</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>61.6</v>
+        <v>60</v>
       </c>
       <c r="E4">
-        <v>97.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="F4">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>87.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NGA-2021-014-1</t>
+          <t>Bangui 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>mOPV</t>
         </is>
       </c>
       <c r="C5">
-        <v>130</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>59.2</v>
+        <v>60</v>
       </c>
       <c r="E5">
-        <v>97.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F5">
-        <v>82.3</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>82.3</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NGA-2021-020-2</t>
+          <t>CAM-2025-08-MAN_-bOPV-sNID</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2038,232 +3340,5394 @@
         </is>
       </c>
       <c r="C6">
-        <v>332</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>58.7</v>
+        <v>60</v>
       </c>
       <c r="E6">
-        <v>96.3</v>
+        <v>97.2</v>
       </c>
       <c r="F6">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>84.09999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NGA-20DS-01-2020</t>
+          <t>CHD-2026-02_nOPV_sNID</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C7">
-        <v>808</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="E7">
-        <v>96.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="F7">
-        <v>79.7</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>79.7</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>87.40000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NIE-2023-07-03_nOPV</t>
+          <t>CIV-2023-06-01_nOPV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fIPV+nOPV2</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C8">
-        <v>253</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>58.4</v>
+        <v>60</v>
       </c>
       <c r="E8">
-        <v>96.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="F8">
-        <v>77.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>77.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>82.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OBR_name</t>
+          <t>DRC-2025-05-R0_nOPV_sNID</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C9">
-        <v>2425</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E9">
-        <v>96.8</v>
+        <v>98.7</v>
       </c>
       <c r="F9">
-        <v>75.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>75.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>86.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NIE-2024-nOPV2</t>
+          <t>DRC-2025-11-01_n-BOPV_sNID</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nOPV2</t>
+          <t>bOPV</t>
         </is>
       </c>
       <c r="C10">
-        <v>1254</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>61.3</v>
+        <v>60</v>
       </c>
       <c r="E10">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>72.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G10">
-        <v>72.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>89.90000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NGA-2021-016-1</t>
+          <t>EXNORD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C11">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>54.3</v>
+        <v>60</v>
       </c>
       <c r="E11">
-        <v>96.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="F11">
-        <v>68.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G11">
-        <v>68.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>83.09999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NGA-2021-013-1</t>
+          <t>KEN-2024-01-01_nOPV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bOPV</t>
+          <t>nOPV2</t>
         </is>
       </c>
       <c r="C12">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="D12">
-        <v>56.1</v>
+        <v>60</v>
       </c>
       <c r="E12">
-        <v>95.5</v>
+        <v>99.8</v>
       </c>
       <c r="F12">
-        <v>64.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G12">
-        <v>64.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>86.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>MopUp2022_nOPV</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>60</v>
+      </c>
+      <c r="E13">
+        <v>99</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NIG-2023-11-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+      <c r="D14">
+        <v>60</v>
+      </c>
+      <c r="E14">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TNZ-2023-07-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>74</v>
+      </c>
+      <c r="D15">
+        <v>60</v>
+      </c>
+      <c r="E15">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>nOPV2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>8</v>
+      </c>
+      <c r="D16">
+        <v>60</v>
+      </c>
+      <c r="E16">
+        <v>98.3</v>
+      </c>
+      <c r="F16">
+        <v>100</v>
+      </c>
+      <c r="G16">
+        <v>100</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BEN-2025-11-01_nOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>76</v>
+      </c>
+      <c r="D17">
+        <v>60.1</v>
+      </c>
+      <c r="E17">
+        <v>98.8</v>
+      </c>
+      <c r="F17">
+        <v>98.7</v>
+      </c>
+      <c r="G17">
+        <v>98.7</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GUI-2025-01-NID_bOPV-nOPV</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>76</v>
+      </c>
+      <c r="D18">
+        <v>60</v>
+      </c>
+      <c r="E18">
+        <v>98.5</v>
+      </c>
+      <c r="F18">
+        <v>98.7</v>
+      </c>
+      <c r="G18">
+        <v>98.7</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BFA-2025-08-01_nOPV_sNIDs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>30</v>
+      </c>
+      <c r="D19">
+        <v>60</v>
+      </c>
+      <c r="E19">
+        <v>98.7</v>
+      </c>
+      <c r="F19">
+        <v>96.7</v>
+      </c>
+      <c r="G19">
+        <v>96.7</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DRC-2026-01-01_nOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>60</v>
+      </c>
+      <c r="E20">
+        <v>98.2</v>
+      </c>
+      <c r="F20">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BFA-2024-10-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>52</v>
+      </c>
+      <c r="D21">
+        <v>59.4</v>
+      </c>
+      <c r="E21">
+        <v>99</v>
+      </c>
+      <c r="F21">
+        <v>96.2</v>
+      </c>
+      <c r="G21">
+        <v>96.2</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BFA-2023-05-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>67</v>
+      </c>
+      <c r="D22">
+        <v>60</v>
+      </c>
+      <c r="E22">
+        <v>99</v>
+      </c>
+      <c r="F22">
+        <v>95.5</v>
+      </c>
+      <c r="G22">
+        <v>95.5</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>nVPO_Maradi</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>42</v>
+      </c>
+      <c r="D23">
+        <v>59.8</v>
+      </c>
+      <c r="E23">
+        <v>98.8</v>
+      </c>
+      <c r="F23">
+        <v>95.2</v>
+      </c>
+      <c r="G23">
+        <v>95.2</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DRC-2026-02-bOPV-nOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>18</v>
+      </c>
+      <c r="D24">
+        <v>58.9</v>
+      </c>
+      <c r="E24">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="F24">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="G24">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ALG-2024-01-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>53</v>
+      </c>
+      <c r="D25">
+        <v>60</v>
+      </c>
+      <c r="E25">
+        <v>98.7</v>
+      </c>
+      <c r="F25">
+        <v>94.3</v>
+      </c>
+      <c r="G25">
+        <v>94.3</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>nVPO_Zinder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>17</v>
+      </c>
+      <c r="D26">
+        <v>60</v>
+      </c>
+      <c r="E26">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="F26">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="G26">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CAM-2024-sNID-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>73</v>
+      </c>
+      <c r="D27">
+        <v>60</v>
+      </c>
+      <c r="E27">
+        <v>97.5</v>
+      </c>
+      <c r="F27">
+        <v>93.2</v>
+      </c>
+      <c r="G27">
+        <v>93.2</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CHD-2023-05-1_nOPV</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>226</v>
+      </c>
+      <c r="D28">
+        <v>59.8</v>
+      </c>
+      <c r="E28">
+        <v>97.7</v>
+      </c>
+      <c r="F28">
+        <v>92.5</v>
+      </c>
+      <c r="G28">
+        <v>92.5</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GUI-2024-10-NID_nOPV</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>38</v>
+      </c>
+      <c r="D29">
+        <v>60</v>
+      </c>
+      <c r="E29">
+        <v>97.8</v>
+      </c>
+      <c r="F29">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G29">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BEN-2025-04-01_nOPV_NIDs</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>172</v>
+      </c>
+      <c r="D30">
+        <v>60</v>
+      </c>
+      <c r="E30">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F30">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G30">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MOZ-2023-03-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>12</v>
+      </c>
+      <c r="D31">
+        <v>60</v>
+      </c>
+      <c r="E31">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F31">
+        <v>91.7</v>
+      </c>
+      <c r="G31">
+        <v>91.7</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TOG-39DS-06-022</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>12</v>
+      </c>
+      <c r="D32">
+        <v>60</v>
+      </c>
+      <c r="E32">
+        <v>99</v>
+      </c>
+      <c r="F32">
+        <v>91.7</v>
+      </c>
+      <c r="G32">
+        <v>91.7</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CIV-2025-02-01_nOPV_NIDs</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>226</v>
+      </c>
+      <c r="D33">
+        <v>60</v>
+      </c>
+      <c r="E33">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F33">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="G33">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NIG-2025-04-01_nOPV_NIDs</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>130</v>
+      </c>
+      <c r="D34">
+        <v>59.9</v>
+      </c>
+      <c r="E34">
+        <v>97.2</v>
+      </c>
+      <c r="F34">
+        <v>91.5</v>
+      </c>
+      <c r="G34">
+        <v>91.5</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ZAM-2026-03-01_nOPV-sNID</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>212</v>
+      </c>
+      <c r="D35">
+        <v>59.9</v>
+      </c>
+      <c r="E35">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="F35">
+        <v>91.5</v>
+      </c>
+      <c r="G35">
+        <v>91.5</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BFA-2024-02-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>56</v>
+      </c>
+      <c r="D36">
+        <v>60</v>
+      </c>
+      <c r="E36">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="F36">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="G36">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DRC-2025-06-01_nOPV_NID</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>393</v>
+      </c>
+      <c r="D37">
+        <v>59.5</v>
+      </c>
+      <c r="E37">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="F37">
+        <v>90.8</v>
+      </c>
+      <c r="G37">
+        <v>90.8</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NIE-2025-04-01_nOPV_NIDs</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>1030</v>
+      </c>
+      <c r="D38">
+        <v>60.1</v>
+      </c>
+      <c r="E38">
+        <v>97.8</v>
+      </c>
+      <c r="F38">
+        <v>90.2</v>
+      </c>
+      <c r="G38">
+        <v>90.2</v>
+      </c>
+      <c r="H38">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CIV-2024-04-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>159</v>
+      </c>
+      <c r="D39">
+        <v>60</v>
+      </c>
+      <c r="E39">
+        <v>97.3</v>
+      </c>
+      <c r="F39">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="G39">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ouagadogou-mOPV2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>mOPV</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>136</v>
+      </c>
+      <c r="D40">
+        <v>60</v>
+      </c>
+      <c r="E40">
+        <v>97</v>
+      </c>
+      <c r="F40">
+        <v>89.7</v>
+      </c>
+      <c r="G40">
+        <v>89.7</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DRC-2025-02-01_nOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>224</v>
+      </c>
+      <c r="D41">
+        <v>59.4</v>
+      </c>
+      <c r="E41">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="F41">
+        <v>89.3</v>
+      </c>
+      <c r="G41">
+        <v>89.3</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NIG-2024-10-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>122</v>
+      </c>
+      <c r="D42">
+        <v>60</v>
+      </c>
+      <c r="E42">
+        <v>97.2</v>
+      </c>
+      <c r="F42">
+        <v>89.3</v>
+      </c>
+      <c r="G42">
+        <v>89.3</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CAM-2023-05-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>146</v>
+      </c>
+      <c r="D43">
+        <v>60</v>
+      </c>
+      <c r="E43">
+        <v>97.5</v>
+      </c>
+      <c r="F43">
+        <v>89</v>
+      </c>
+      <c r="G43">
+        <v>89</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MOZ-2024-04-01_bOPV</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>91</v>
+      </c>
+      <c r="D44">
+        <v>60</v>
+      </c>
+      <c r="E44">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="F44">
+        <v>89</v>
+      </c>
+      <c r="G44">
+        <v>89</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chavuma-mOPV</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>mOPV</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>9</v>
+      </c>
+      <c r="D45">
+        <v>58.9</v>
+      </c>
+      <c r="E45">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="F45">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="G45">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CENBLOCK-nOPV</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>266</v>
+      </c>
+      <c r="D46">
+        <v>59.8</v>
+      </c>
+      <c r="E46">
+        <v>97.3</v>
+      </c>
+      <c r="F46">
+        <v>88.7</v>
+      </c>
+      <c r="G46">
+        <v>88.7</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>KEN-2024-11-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>71</v>
+      </c>
+      <c r="D47">
+        <v>60</v>
+      </c>
+      <c r="E47">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="F47">
+        <v>88.7</v>
+      </c>
+      <c r="G47">
+        <v>88.7</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MDG-2024-05-01_bOPV</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>228</v>
+      </c>
+      <c r="D48">
+        <v>60.2</v>
+      </c>
+      <c r="E48">
+        <v>96.8</v>
+      </c>
+      <c r="F48">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="G48">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ZAM-2023-02-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>88</v>
+      </c>
+      <c r="D49">
+        <v>60</v>
+      </c>
+      <c r="E49">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F49">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="G49">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ZAM-2024-06-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>44</v>
+      </c>
+      <c r="D50">
+        <v>60</v>
+      </c>
+      <c r="E50">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="F50">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="G50">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TOG-2025-11-01_nOPV_sNIDs</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>78</v>
+      </c>
+      <c r="D51">
+        <v>60</v>
+      </c>
+      <c r="E51">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F51">
+        <v>88.5</v>
+      </c>
+      <c r="G51">
+        <v>88.5</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ZAM-2023-09-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>168</v>
+      </c>
+      <c r="D52">
+        <v>60</v>
+      </c>
+      <c r="E52">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="F52">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="G52">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ALG-2025-09-01_nOPV_NID</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>548</v>
+      </c>
+      <c r="D53">
+        <v>61.1</v>
+      </c>
+      <c r="E53">
+        <v>97.7</v>
+      </c>
+      <c r="F53">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="G53">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CAR-2023-05-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>56</v>
+      </c>
+      <c r="D54">
+        <v>60</v>
+      </c>
+      <c r="E54">
+        <v>96.3</v>
+      </c>
+      <c r="F54">
+        <v>87.5</v>
+      </c>
+      <c r="G54">
+        <v>87.5</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ExtNord2023</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>16</v>
+      </c>
+      <c r="D55">
+        <v>60</v>
+      </c>
+      <c r="E55">
+        <v>97.5</v>
+      </c>
+      <c r="F55">
+        <v>87.5</v>
+      </c>
+      <c r="G55">
+        <v>87.5</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RCA-2026-03_nOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>24</v>
+      </c>
+      <c r="D56">
+        <v>59.6</v>
+      </c>
+      <c r="E56">
+        <v>96.7</v>
+      </c>
+      <c r="F56">
+        <v>87.5</v>
+      </c>
+      <c r="G56">
+        <v>87.5</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NIG-2023-05-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>102</v>
+      </c>
+      <c r="D57">
+        <v>59.7</v>
+      </c>
+      <c r="E57">
+        <v>96</v>
+      </c>
+      <c r="F57">
+        <v>87.3</v>
+      </c>
+      <c r="G57">
+        <v>87.3</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DRC-2026-03-NID_bOPV-nOPV</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>917</v>
+      </c>
+      <c r="D58">
+        <v>59</v>
+      </c>
+      <c r="E58">
+        <v>97.7</v>
+      </c>
+      <c r="F58">
+        <v>87.2</v>
+      </c>
+      <c r="G58">
+        <v>87.2</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ANG-2026-08-02_nOPV_NID</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>325</v>
+      </c>
+      <c r="D59">
+        <v>60.3</v>
+      </c>
+      <c r="E59">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F59">
+        <v>86.5</v>
+      </c>
+      <c r="G59">
+        <v>86.5</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NIE-2023-07-03_nOPV</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>728</v>
+      </c>
+      <c r="D60">
+        <v>59.4</v>
+      </c>
+      <c r="E60">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="F60">
+        <v>86</v>
+      </c>
+      <c r="G60">
+        <v>86</v>
+      </c>
+      <c r="H60">
+        <v>87.59999999999999</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DRC-2025-11-01_n-BOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>406</v>
+      </c>
+      <c r="D61">
+        <v>58.2</v>
+      </c>
+      <c r="E61">
+        <v>97.8</v>
+      </c>
+      <c r="F61">
+        <v>85.7</v>
+      </c>
+      <c r="G61">
+        <v>85.7</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DRC-2024-10-01_B_nOPV</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>429</v>
+      </c>
+      <c r="D62">
+        <v>58.4</v>
+      </c>
+      <c r="E62">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F62">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="G62">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CHD-2025-10-0n_bOPV-NIDs</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>357</v>
+      </c>
+      <c r="D63">
+        <v>60</v>
+      </c>
+      <c r="E63">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="F63">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="G63">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>NIG-2025-10-01_nOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>46</v>
+      </c>
+      <c r="D64">
+        <v>60</v>
+      </c>
+      <c r="E64">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="F64">
+        <v>84.8</v>
+      </c>
+      <c r="G64">
+        <v>84.8</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CNG-2024-08-BOPV</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>52</v>
+      </c>
+      <c r="D65">
+        <v>60</v>
+      </c>
+      <c r="E65">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="F65">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="G65">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ZAM-2023-05-01_bOPV</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>116</v>
+      </c>
+      <c r="D66">
+        <v>60</v>
+      </c>
+      <c r="E66">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="F66">
+        <v>84.5</v>
+      </c>
+      <c r="G66">
+        <v>84.5</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>OBR_name</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>797</v>
+      </c>
+      <c r="D67">
+        <v>61.6</v>
+      </c>
+      <c r="E67">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F67">
+        <v>84.2</v>
+      </c>
+      <c r="G67">
+        <v>84.2</v>
+      </c>
+      <c r="H67">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BEN-xxDS-02-2020</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>mOPV</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>30</v>
+      </c>
+      <c r="D68">
+        <v>60</v>
+      </c>
+      <c r="E68">
+        <v>97.3</v>
+      </c>
+      <c r="F68">
+        <v>83.3</v>
+      </c>
+      <c r="G68">
+        <v>83.3</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CAM-2025-11-01_n_bOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>148</v>
+      </c>
+      <c r="D69">
+        <v>60</v>
+      </c>
+      <c r="E69">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="F69">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="G69">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>NGA-2021-014-1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>130</v>
+      </c>
+      <c r="D70">
+        <v>59.2</v>
+      </c>
+      <c r="E70">
+        <v>97.2</v>
+      </c>
+      <c r="F70">
+        <v>82.3</v>
+      </c>
+      <c r="G70">
+        <v>82.3</v>
+      </c>
+      <c r="H70">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>NIG-2024-06-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>117</v>
+      </c>
+      <c r="D71">
+        <v>59.7</v>
+      </c>
+      <c r="E71">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="F71">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="G71">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>NGA-2021-020-2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>332</v>
+      </c>
+      <c r="D72">
+        <v>58.7</v>
+      </c>
+      <c r="E72">
+        <v>96.3</v>
+      </c>
+      <c r="F72">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G72">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="H72">
+        <v>84.09999999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CAF-2020-002</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>mOPV</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>11</v>
+      </c>
+      <c r="D73">
+        <v>60</v>
+      </c>
+      <c r="E73">
+        <v>97.3</v>
+      </c>
+      <c r="F73">
+        <v>81.8</v>
+      </c>
+      <c r="G73">
+        <v>81.8</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>GUI-2024-06-LIDs_nOPV</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>21</v>
+      </c>
+      <c r="D74">
+        <v>60</v>
+      </c>
+      <c r="E74">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F74">
+        <v>81</v>
+      </c>
+      <c r="G74">
+        <v>81</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MLW-2023-04-1_bOPV</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>58</v>
+      </c>
+      <c r="D75">
+        <v>60</v>
+      </c>
+      <c r="E75">
+        <v>96</v>
+      </c>
+      <c r="F75">
+        <v>81</v>
+      </c>
+      <c r="G75">
+        <v>81</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>NIG-2026-03_nOPV_NIDs</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>125</v>
+      </c>
+      <c r="D76">
+        <v>59.9</v>
+      </c>
+      <c r="E76">
+        <v>95.3</v>
+      </c>
+      <c r="F76">
+        <v>80.8</v>
+      </c>
+      <c r="G76">
+        <v>80.8</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ETH-2026-03-nOPV2-sNID</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>108</v>
+      </c>
+      <c r="D77">
+        <v>139.3</v>
+      </c>
+      <c r="E77">
+        <v>98.5</v>
+      </c>
+      <c r="F77">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="G77">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>RWA-2023-07-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>60</v>
+      </c>
+      <c r="D78">
+        <v>92</v>
+      </c>
+      <c r="E78">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F78">
+        <v>80</v>
+      </c>
+      <c r="G78">
+        <v>80</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ZIM-2024-11-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>150</v>
+      </c>
+      <c r="D79">
+        <v>59.6</v>
+      </c>
+      <c r="E79">
+        <v>96.7</v>
+      </c>
+      <c r="F79">
+        <v>80</v>
+      </c>
+      <c r="G79">
+        <v>80</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>NGA-20DS-01-2020</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>808</v>
+      </c>
+      <c r="D80">
+        <v>59.9</v>
+      </c>
+      <c r="E80">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="F80">
+        <v>79.7</v>
+      </c>
+      <c r="G80">
+        <v>79.7</v>
+      </c>
+      <c r="H80">
+        <v>87.40000000000001</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>GNBnOPV</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>43</v>
+      </c>
+      <c r="D81">
+        <v>60</v>
+      </c>
+      <c r="E81">
+        <v>96</v>
+      </c>
+      <c r="F81">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="G81">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>GOTHEYE-mOPV</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>mOPV</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>47</v>
+      </c>
+      <c r="D82">
+        <v>59.6</v>
+      </c>
+      <c r="E82">
+        <v>95.8</v>
+      </c>
+      <c r="F82">
+        <v>78.7</v>
+      </c>
+      <c r="G82">
+        <v>78.7</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ANG-2025-05-01_nOPV-sNID</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>46</v>
+      </c>
+      <c r="D83">
+        <v>60</v>
+      </c>
+      <c r="E83">
+        <v>94.7</v>
+      </c>
+      <c r="F83">
+        <v>78.3</v>
+      </c>
+      <c r="G83">
+        <v>78.3</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>NIE-2023-07-03_nOPV</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>fIPV+nOPV2</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>253</v>
+      </c>
+      <c r="D84">
+        <v>58.4</v>
+      </c>
+      <c r="E84">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="F84">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="G84">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="H84">
+        <v>82.59999999999999</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>RCA-2025-10-01_nOPV_NIDs</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>63</v>
+      </c>
+      <c r="D85">
+        <v>60</v>
+      </c>
+      <c r="E85">
+        <v>94.7</v>
+      </c>
+      <c r="F85">
+        <v>77.8</v>
+      </c>
+      <c r="G85">
+        <v>77.8</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CAR-2024-02-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>62</v>
+      </c>
+      <c r="D86">
+        <v>59.4</v>
+      </c>
+      <c r="E86">
+        <v>95.7</v>
+      </c>
+      <c r="F86">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="G86">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CAR-2024-sNIDs-11_nOPV</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>22</v>
+      </c>
+      <c r="D87">
+        <v>57.3</v>
+      </c>
+      <c r="E87">
+        <v>97</v>
+      </c>
+      <c r="F87">
+        <v>77.3</v>
+      </c>
+      <c r="G87">
+        <v>77.3</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CHD-2023-10-1_nOPV</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>339</v>
+      </c>
+      <c r="D88">
+        <v>60</v>
+      </c>
+      <c r="E88">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="F88">
+        <v>77.3</v>
+      </c>
+      <c r="G88">
+        <v>77.3</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>RCA-2025-04-01_nOPV_NIDs</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>66</v>
+      </c>
+      <c r="D89">
+        <v>59.2</v>
+      </c>
+      <c r="E89">
+        <v>96.2</v>
+      </c>
+      <c r="F89">
+        <v>77.3</v>
+      </c>
+      <c r="G89">
+        <v>77.3</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ANG-2026-02-01_nOPV-sNID</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>13</v>
+      </c>
+      <c r="D90">
+        <v>60</v>
+      </c>
+      <c r="E90">
+        <v>95.8</v>
+      </c>
+      <c r="F90">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G90">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CAM-2026-03_nOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>260</v>
+      </c>
+      <c r="D91">
+        <v>60</v>
+      </c>
+      <c r="E91">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="F91">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G91">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>bOPV Rnd 2 ETH-2026-05-bOPV2-sNID</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>13</v>
+      </c>
+      <c r="D92">
+        <v>103.8</v>
+      </c>
+      <c r="E92">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F92">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G92">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ANG-2026-03-01_nOPV_NID</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>650</v>
+      </c>
+      <c r="D93">
+        <v>59.8</v>
+      </c>
+      <c r="E93">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F93">
+        <v>76</v>
+      </c>
+      <c r="G93">
+        <v>76</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CAM-2025-04-01_nOPV_NIDs</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>325</v>
+      </c>
+      <c r="D94">
+        <v>60</v>
+      </c>
+      <c r="E94">
+        <v>94.7</v>
+      </c>
+      <c r="F94">
+        <v>76</v>
+      </c>
+      <c r="G94">
+        <v>76</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ZIM-2023-12-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>150</v>
+      </c>
+      <c r="D95">
+        <v>59.5</v>
+      </c>
+      <c r="E95">
+        <v>95.8</v>
+      </c>
+      <c r="F95">
+        <v>76</v>
+      </c>
+      <c r="G95">
+        <v>76</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>LBR-2024-05-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>291</v>
+      </c>
+      <c r="D96">
+        <v>58.9</v>
+      </c>
+      <c r="E96">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="F96">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="G96">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MOZ-2025-05-1_nOPV_NID</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>318</v>
+      </c>
+      <c r="D97">
+        <v>59.9</v>
+      </c>
+      <c r="E97">
+        <v>93</v>
+      </c>
+      <c r="F97">
+        <v>75.8</v>
+      </c>
+      <c r="G97">
+        <v>75.8</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>OBR_name</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>2425</v>
+      </c>
+      <c r="D98">
+        <v>73</v>
+      </c>
+      <c r="E98">
+        <v>96.8</v>
+      </c>
+      <c r="F98">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G98">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="H98">
+        <v>86.2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CAR-2024-sNIDs-09_nOPV</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>8</v>
+      </c>
+      <c r="D99">
+        <v>60</v>
+      </c>
+      <c r="E99">
+        <v>96.5</v>
+      </c>
+      <c r="F99">
+        <v>75</v>
+      </c>
+      <c r="G99">
+        <v>75</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CHD-2026-03_nOPV_NID</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>391</v>
+      </c>
+      <c r="D100">
+        <v>60</v>
+      </c>
+      <c r="E100">
+        <v>94</v>
+      </c>
+      <c r="F100">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="G100">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CIV-2023-09-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>227</v>
+      </c>
+      <c r="D101">
+        <v>59.6</v>
+      </c>
+      <c r="E101">
+        <v>95.3</v>
+      </c>
+      <c r="F101">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="G101">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MDG-2023-03-01_bOPV</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>452</v>
+      </c>
+      <c r="D102">
+        <v>58.4</v>
+      </c>
+      <c r="E102">
+        <v>95.2</v>
+      </c>
+      <c r="F102">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="G102">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MLW_WPV1</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>1313</v>
+      </c>
+      <c r="D103">
+        <v>59.8</v>
+      </c>
+      <c r="E103">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F103">
+        <v>74.2</v>
+      </c>
+      <c r="G103">
+        <v>74.2</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>159</v>
+      </c>
+      <c r="D104">
+        <v>59</v>
+      </c>
+      <c r="E104">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="F104">
+        <v>74.2</v>
+      </c>
+      <c r="G104">
+        <v>74.2</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ALG-2023-09-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>53</v>
+      </c>
+      <c r="D105">
+        <v>60</v>
+      </c>
+      <c r="E105">
+        <v>95.2</v>
+      </c>
+      <c r="F105">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="G105">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>BUU-2023-04-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>147</v>
+      </c>
+      <c r="D106">
+        <v>60</v>
+      </c>
+      <c r="E106">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="F106">
+        <v>73.5</v>
+      </c>
+      <c r="G106">
+        <v>73.5</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NIE-2024-nOPV2</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>1254</v>
+      </c>
+      <c r="D107">
+        <v>61.3</v>
+      </c>
+      <c r="E107">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F107">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="G107">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="H107">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>GUI-2026-01-SNID-bOPV_nOPV</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>18</v>
+      </c>
+      <c r="D108">
+        <v>59.4</v>
+      </c>
+      <c r="E108">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="F108">
+        <v>72.2</v>
+      </c>
+      <c r="G108">
+        <v>72.2</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ZIM-2026-03-01_nOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>90</v>
+      </c>
+      <c r="D109">
+        <v>57.9</v>
+      </c>
+      <c r="E109">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="F109">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="G109">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ETH-2024-08-nOPV2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>24</v>
+      </c>
+      <c r="D110">
+        <v>228.8</v>
+      </c>
+      <c r="E110">
+        <v>96.7</v>
+      </c>
+      <c r="F110">
+        <v>70.8</v>
+      </c>
+      <c r="G110">
+        <v>70.8</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MOZ-2023-05-01_bOPV</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>322</v>
+      </c>
+      <c r="D111">
+        <v>60</v>
+      </c>
+      <c r="E111">
+        <v>91.2</v>
+      </c>
+      <c r="F111">
+        <v>70.5</v>
+      </c>
+      <c r="G111">
+        <v>70.5</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>CNG-2023-10-nOPV</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>104</v>
+      </c>
+      <c r="D112">
+        <v>59.9</v>
+      </c>
+      <c r="E112">
+        <v>91</v>
+      </c>
+      <c r="F112">
+        <v>69.2</v>
+      </c>
+      <c r="G112">
+        <v>69.2</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ANG-2025-08-01_nOPV-NID</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>622</v>
+      </c>
+      <c r="D113">
+        <v>59.9</v>
+      </c>
+      <c r="E113">
+        <v>94.3</v>
+      </c>
+      <c r="F113">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="G113">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CHA-17DS-02-2020</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>16</v>
+      </c>
+      <c r="D114">
+        <v>59.4</v>
+      </c>
+      <c r="E114">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="F114">
+        <v>68.8</v>
+      </c>
+      <c r="G114">
+        <v>68.8</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>NGA-2021-016-1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>51</v>
+      </c>
+      <c r="D115">
+        <v>54.3</v>
+      </c>
+      <c r="E115">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="F115">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="G115">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="H115">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CAM-2024-10-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>161</v>
+      </c>
+      <c r="D116">
+        <v>60</v>
+      </c>
+      <c r="E116">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="F116">
+        <v>68.3</v>
+      </c>
+      <c r="G116">
+        <v>68.3</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CENTRALBLK</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>50</v>
+      </c>
+      <c r="D117">
+        <v>57.6</v>
+      </c>
+      <c r="E117">
+        <v>96</v>
+      </c>
+      <c r="F117">
+        <v>68</v>
+      </c>
+      <c r="G117">
+        <v>68</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DONOMANGA</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>150</v>
+      </c>
+      <c r="D118">
+        <v>59.9</v>
+      </c>
+      <c r="E118">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="F118">
+        <v>67.3</v>
+      </c>
+      <c r="G118">
+        <v>67.3</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>YOPOUGON EST</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>mOPV</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>227</v>
+      </c>
+      <c r="D119">
+        <v>59.3</v>
+      </c>
+      <c r="E119">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="F119">
+        <v>67</v>
+      </c>
+      <c r="G119">
+        <v>67</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>nOPV2022</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>922</v>
+      </c>
+      <c r="D120">
+        <v>59.6</v>
+      </c>
+      <c r="E120">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="F120">
+        <v>66.3</v>
+      </c>
+      <c r="G120">
+        <v>66.3</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ETH-2025-10-b-nOPV2-sNID</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>29</v>
+      </c>
+      <c r="D121">
+        <v>143.4</v>
+      </c>
+      <c r="E121">
+        <v>97.3</v>
+      </c>
+      <c r="F121">
+        <v>65.5</v>
+      </c>
+      <c r="G121">
+        <v>65.5</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>EBOLOWA</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>20</v>
+      </c>
+      <c r="D122">
+        <v>60</v>
+      </c>
+      <c r="E122">
+        <v>92.8</v>
+      </c>
+      <c r="F122">
+        <v>65</v>
+      </c>
+      <c r="G122">
+        <v>65</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ETH-2025-12-b-nOPV2-NIDs</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>143</v>
+      </c>
+      <c r="D123">
+        <v>151.3</v>
+      </c>
+      <c r="E123">
+        <v>97.7</v>
+      </c>
+      <c r="F123">
+        <v>65</v>
+      </c>
+      <c r="G123">
+        <v>65</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>GHA-2024-10-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>534</v>
+      </c>
+      <c r="D124">
+        <v>60</v>
+      </c>
+      <c r="E124">
+        <v>93.7</v>
+      </c>
+      <c r="F124">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="G124">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>NGA-2021-013-1</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>130</v>
+      </c>
+      <c r="D125">
+        <v>56.1</v>
+      </c>
+      <c r="E125">
+        <v>95.5</v>
+      </c>
+      <c r="F125">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="G125">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="H125">
+        <v>86.59999999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AMANSIE SOUTH</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>358</v>
+      </c>
+      <c r="D126">
+        <v>59.9</v>
+      </c>
+      <c r="E126">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="F126">
+        <v>64.5</v>
+      </c>
+      <c r="G126">
+        <v>64.5</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NAM-2025-12-n_OPV-NIDs</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>115</v>
+      </c>
+      <c r="D127">
+        <v>59.9</v>
+      </c>
+      <c r="E127">
+        <v>93</v>
+      </c>
+      <c r="F127">
+        <v>64.3</v>
+      </c>
+      <c r="G127">
+        <v>64.3</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>WPV1MLW</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>504</v>
+      </c>
+      <c r="D128">
+        <v>59.5</v>
+      </c>
+      <c r="E128">
+        <v>93.7</v>
+      </c>
+      <c r="F128">
+        <v>63.7</v>
+      </c>
+      <c r="G128">
+        <v>63.7</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>BOT-2023-02-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>54</v>
+      </c>
+      <c r="D129">
+        <v>60</v>
+      </c>
+      <c r="E129">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="F129">
+        <v>63</v>
+      </c>
+      <c r="G129">
+        <v>63</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CAM-2024-02-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>161</v>
+      </c>
+      <c r="D130">
+        <v>59.9</v>
+      </c>
+      <c r="E130">
+        <v>93</v>
+      </c>
+      <c r="F130">
+        <v>62.7</v>
+      </c>
+      <c r="G130">
+        <v>62.7</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>40</v>
+      </c>
+      <c r="D131">
+        <v>51.2</v>
+      </c>
+      <c r="E131">
+        <v>95</v>
+      </c>
+      <c r="F131">
+        <v>62.5</v>
+      </c>
+      <c r="G131">
+        <v>62.5</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>BEN-2023-09-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>45</v>
+      </c>
+      <c r="D132">
+        <v>57.8</v>
+      </c>
+      <c r="E132">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F132">
+        <v>62.2</v>
+      </c>
+      <c r="G132">
+        <v>62.2</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CAM-2023-08-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>248</v>
+      </c>
+      <c r="D133">
+        <v>59.7</v>
+      </c>
+      <c r="E133">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="F133">
+        <v>62.1</v>
+      </c>
+      <c r="G133">
+        <v>62.1</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>KEN-2023-08-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>177</v>
+      </c>
+      <c r="D134">
+        <v>60</v>
+      </c>
+      <c r="E134">
+        <v>92.7</v>
+      </c>
+      <c r="F134">
+        <v>61.6</v>
+      </c>
+      <c r="G134">
+        <v>61.6</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>UGA-2024-08-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>98</v>
+      </c>
+      <c r="D135">
+        <v>59.9</v>
+      </c>
+      <c r="E135">
+        <v>92.7</v>
+      </c>
+      <c r="F135">
+        <v>61.2</v>
+      </c>
+      <c r="G135">
+        <v>61.2</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TNZ-2026-02-01_nOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>100</v>
+      </c>
+      <c r="D136">
+        <v>57.4</v>
+      </c>
+      <c r="E136">
+        <v>94</v>
+      </c>
+      <c r="F136">
+        <v>61</v>
+      </c>
+      <c r="G136">
+        <v>61</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MLW-2026-02-1_nOPV</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>124</v>
+      </c>
+      <c r="D137">
+        <v>60</v>
+      </c>
+      <c r="E137">
+        <v>93.7</v>
+      </c>
+      <c r="F137">
+        <v>59.7</v>
+      </c>
+      <c r="G137">
+        <v>59.7</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>KEN-2024-08-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>142</v>
+      </c>
+      <c r="D138">
+        <v>60</v>
+      </c>
+      <c r="E138">
+        <v>93.2</v>
+      </c>
+      <c r="F138">
+        <v>59.2</v>
+      </c>
+      <c r="G138">
+        <v>59.2</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ETH-2026-05-bOPV-sNID</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>22</v>
+      </c>
+      <c r="D139">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="E139">
+        <v>96.5</v>
+      </c>
+      <c r="F139">
+        <v>59.1</v>
+      </c>
+      <c r="G139">
+        <v>59.1</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ETH-2024-11-nOPV2_sNID</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>204</v>
+      </c>
+      <c r="D140">
+        <v>165.2</v>
+      </c>
+      <c r="E140">
+        <v>96.3</v>
+      </c>
+      <c r="F140">
+        <v>58.3</v>
+      </c>
+      <c r="G140">
+        <v>58.3</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SSD-2026-01-05_nOPV2</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>33</v>
+      </c>
+      <c r="D141">
+        <v>60</v>
+      </c>
+      <c r="E141">
+        <v>93.5</v>
+      </c>
+      <c r="F141">
+        <v>57.6</v>
+      </c>
+      <c r="G141">
+        <v>57.6</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ANGOLA-NID-2024-nOPV2</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>356</v>
+      </c>
+      <c r="D142">
+        <v>59.9</v>
+      </c>
+      <c r="E142">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="F142">
+        <v>56.7</v>
+      </c>
+      <c r="G142">
+        <v>56.7</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>BEN-26DS-08-2020</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>23</v>
+      </c>
+      <c r="D143">
+        <v>58.7</v>
+      </c>
+      <c r="E143">
+        <v>94.2</v>
+      </c>
+      <c r="F143">
+        <v>56.5</v>
+      </c>
+      <c r="G143">
+        <v>56.5</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ZIM-2023-05-01_bOPV</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>149</v>
+      </c>
+      <c r="D144">
+        <v>59.9</v>
+      </c>
+      <c r="E144">
+        <v>93.3</v>
+      </c>
+      <c r="F144">
+        <v>56.4</v>
+      </c>
+      <c r="G144">
+        <v>56.4</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SLE-2024-05-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>48</v>
+      </c>
+      <c r="D145">
+        <v>59.4</v>
+      </c>
+      <c r="E145">
+        <v>91.5</v>
+      </c>
+      <c r="F145">
+        <v>56.2</v>
+      </c>
+      <c r="G145">
+        <v>56.2</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CHD-2024-11-1_nOPV</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>157</v>
+      </c>
+      <c r="D146">
+        <v>60</v>
+      </c>
+      <c r="E146">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="F146">
+        <v>56.1</v>
+      </c>
+      <c r="G146">
+        <v>56.1</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CHD-2025-05-1_nOPV_NID</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>356</v>
+      </c>
+      <c r="D147">
+        <v>60</v>
+      </c>
+      <c r="E147">
+        <v>89.7</v>
+      </c>
+      <c r="F147">
+        <v>55.6</v>
+      </c>
+      <c r="G147">
+        <v>55.6</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Luapula-mOPV</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>mOPV</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>20</v>
+      </c>
+      <c r="D148">
+        <v>57</v>
+      </c>
+      <c r="E148">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="F148">
+        <v>55</v>
+      </c>
+      <c r="G148">
+        <v>55</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>GOLFE</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>26</v>
+      </c>
+      <c r="D149">
+        <v>59.2</v>
+      </c>
+      <c r="E149">
+        <v>88.2</v>
+      </c>
+      <c r="F149">
+        <v>53.8</v>
+      </c>
+      <c r="G149">
+        <v>53.8</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>OPVb2022</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>39</v>
+      </c>
+      <c r="D150">
+        <v>60</v>
+      </c>
+      <c r="E150">
+        <v>89.3</v>
+      </c>
+      <c r="F150">
+        <v>53.8</v>
+      </c>
+      <c r="G150">
+        <v>53.8</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Sierra Leone</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>28</v>
+      </c>
+      <c r="D151">
+        <v>60</v>
+      </c>
+      <c r="E151">
+        <v>90.2</v>
+      </c>
+      <c r="F151">
+        <v>53.6</v>
+      </c>
+      <c r="G151">
+        <v>53.6</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ANGOLA-SNID-2024-07-nOPV2</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>88</v>
+      </c>
+      <c r="D152">
+        <v>59.9</v>
+      </c>
+      <c r="E152">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="F152">
+        <v>53.4</v>
+      </c>
+      <c r="G152">
+        <v>53.4</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>OPVb2021</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>60</v>
+      </c>
+      <c r="D153">
+        <v>59.7</v>
+      </c>
+      <c r="E153">
+        <v>91.2</v>
+      </c>
+      <c r="F153">
+        <v>53.3</v>
+      </c>
+      <c r="G153">
+        <v>53.3</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>SEN_VPOn</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>158</v>
+      </c>
+      <c r="D154">
+        <v>59.7</v>
+      </c>
+      <c r="E154">
+        <v>90.3</v>
+      </c>
+      <c r="F154">
+        <v>53.2</v>
+      </c>
+      <c r="G154">
+        <v>53.2</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CENBLOCK</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>379</v>
+      </c>
+      <c r="D155">
+        <v>59.8</v>
+      </c>
+      <c r="E155">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="F155">
+        <v>52.5</v>
+      </c>
+      <c r="G155">
+        <v>52.5</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>NGA-2021-011-1</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>bOPV</t>
         </is>
       </c>
-      <c r="C13">
+      <c r="C156">
         <v>40</v>
       </c>
-      <c r="D13">
+      <c r="D156">
         <v>56</v>
       </c>
-      <c r="E13">
+      <c r="E156">
         <v>95.8</v>
       </c>
-      <c r="F13">
+      <c r="F156">
         <v>52.5</v>
       </c>
-      <c r="G13">
+      <c r="G156">
         <v>52.5</v>
       </c>
-      <c r="H13">
+      <c r="H156">
         <v>79</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>KEN-13DS-02-2021</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>mOPV</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>92</v>
+      </c>
+      <c r="D157">
+        <v>60</v>
+      </c>
+      <c r="E157">
+        <v>91.3</v>
+      </c>
+      <c r="F157">
+        <v>52.2</v>
+      </c>
+      <c r="G157">
+        <v>52.2</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SSD-2024-10-01_nOPV2</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>79</v>
+      </c>
+      <c r="D158">
+        <v>60.1</v>
+      </c>
+      <c r="E158">
+        <v>90</v>
+      </c>
+      <c r="F158">
+        <v>51.9</v>
+      </c>
+      <c r="G158">
+        <v>51.9</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>BERTOUA</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>232</v>
+      </c>
+      <c r="D159">
+        <v>59.9</v>
+      </c>
+      <c r="E159">
+        <v>90.3</v>
+      </c>
+      <c r="F159">
+        <v>51.3</v>
+      </c>
+      <c r="G159">
+        <v>51.3</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CAM-2025-08-01_bOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>4</v>
+      </c>
+      <c r="D160">
+        <v>60</v>
+      </c>
+      <c r="E160">
+        <v>91.7</v>
+      </c>
+      <c r="F160">
+        <v>50</v>
+      </c>
+      <c r="G160">
+        <v>50</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>CONAKRY-mOPV</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>mOPV</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>40</v>
+      </c>
+      <c r="D161">
+        <v>59.5</v>
+      </c>
+      <c r="E161">
+        <v>87.3</v>
+      </c>
+      <c r="F161">
+        <v>50</v>
+      </c>
+      <c r="G161">
+        <v>50</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>VPOb</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>2</v>
+      </c>
+      <c r="D162">
+        <v>60</v>
+      </c>
+      <c r="E162">
+        <v>93.3</v>
+      </c>
+      <c r="F162">
+        <v>50</v>
+      </c>
+      <c r="G162">
+        <v>50</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>RSSmOPV10C2021</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>53</v>
+      </c>
+      <c r="D163">
+        <v>58.1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F163">
+        <v>49.1</v>
+      </c>
+      <c r="G163">
+        <v>49.1</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>MOZ-2025-10-1_nOPV_sNID</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>127</v>
+      </c>
+      <c r="D164">
+        <v>60.5</v>
+      </c>
+      <c r="E164">
+        <v>83.8</v>
+      </c>
+      <c r="F164">
+        <v>46.5</v>
+      </c>
+      <c r="G164">
+        <v>46.5</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MAU_57DS_08-2021nOPV</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>130</v>
+      </c>
+      <c r="D165">
+        <v>59.4</v>
+      </c>
+      <c r="E165">
+        <v>81</v>
+      </c>
+      <c r="F165">
+        <v>45.4</v>
+      </c>
+      <c r="G165">
+        <v>45.4</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>BOT-2026-02-1_nOPV_NID</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>62</v>
+      </c>
+      <c r="D166">
+        <v>59.2</v>
+      </c>
+      <c r="E166">
+        <v>89.3</v>
+      </c>
+      <c r="F166">
+        <v>45.2</v>
+      </c>
+      <c r="G166">
+        <v>45.2</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ETH-2024-03-nOPV2</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>9</v>
+      </c>
+      <c r="D167">
+        <v>132.2</v>
+      </c>
+      <c r="E167">
+        <v>94.2</v>
+      </c>
+      <c r="F167">
+        <v>44.4</v>
+      </c>
+      <c r="G167">
+        <v>44.4</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>WPV1Response</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>116</v>
+      </c>
+      <c r="D168">
+        <v>60</v>
+      </c>
+      <c r="E168">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="F168">
+        <v>43.1</v>
+      </c>
+      <c r="G168">
+        <v>43.1</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ADDIS ABABA</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>86</v>
+      </c>
+      <c r="D169">
+        <v>203.7</v>
+      </c>
+      <c r="E169">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="F169">
+        <v>43</v>
+      </c>
+      <c r="G169">
+        <v>43</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>SSD-2024-02-01_nOPV2</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>79</v>
+      </c>
+      <c r="D170">
+        <v>59.9</v>
+      </c>
+      <c r="E170">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="F170">
+        <v>43</v>
+      </c>
+      <c r="G170">
+        <v>43</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CAE-31DS-Sept-2021</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>177</v>
+      </c>
+      <c r="D171">
+        <v>60</v>
+      </c>
+      <c r="E171">
+        <v>84</v>
+      </c>
+      <c r="F171">
+        <v>41.8</v>
+      </c>
+      <c r="G171">
+        <v>41.8</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SSD-79DS-09-2020</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>32</v>
+      </c>
+      <c r="D172">
+        <v>59.7</v>
+      </c>
+      <c r="E172">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="F172">
+        <v>40.6</v>
+      </c>
+      <c r="G172">
+        <v>40.6</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>RSS-2025-08-01_nOPV-sNID</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>40</v>
+      </c>
+      <c r="D173">
+        <v>58</v>
+      </c>
+      <c r="E173">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="F173">
+        <v>40</v>
+      </c>
+      <c r="G173">
+        <v>40</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>UGAnOPV</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>230</v>
+      </c>
+      <c r="D174">
+        <v>60</v>
+      </c>
+      <c r="E174">
+        <v>86.7</v>
+      </c>
+      <c r="F174">
+        <v>39.6</v>
+      </c>
+      <c r="G174">
+        <v>39.6</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>KANKAN-mOPV</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>mOPV</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>36</v>
+      </c>
+      <c r="D175">
+        <v>59.7</v>
+      </c>
+      <c r="E175">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="F175">
+        <v>38.9</v>
+      </c>
+      <c r="G175">
+        <v>38.9</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>GUI-2023-09-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>81</v>
+      </c>
+      <c r="D176">
+        <v>59.9</v>
+      </c>
+      <c r="E176">
+        <v>88.2</v>
+      </c>
+      <c r="F176">
+        <v>38.3</v>
+      </c>
+      <c r="G176">
+        <v>38.3</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CNG-2023-05-bOPV</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>104</v>
+      </c>
+      <c r="D177">
+        <v>58.8</v>
+      </c>
+      <c r="E177">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="F177">
+        <v>37.5</v>
+      </c>
+      <c r="G177">
+        <v>37.5</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>MAU-2024-01-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>124</v>
+      </c>
+      <c r="D178">
+        <v>60</v>
+      </c>
+      <c r="E178">
+        <v>82</v>
+      </c>
+      <c r="F178">
+        <v>34.7</v>
+      </c>
+      <c r="G178">
+        <v>34.7</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>DRC-2025-11-01_n-bOPV_NID</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>nOPV2 &amp; bOPV</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>24</v>
+      </c>
+      <c r="D179">
+        <v>42.5</v>
+      </c>
+      <c r="E179">
+        <v>99.5</v>
+      </c>
+      <c r="F179">
+        <v>33.3</v>
+      </c>
+      <c r="G179">
+        <v>33.3</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>nVPO</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>101</v>
+      </c>
+      <c r="D180">
+        <v>59.3</v>
+      </c>
+      <c r="E180">
+        <v>83.2</v>
+      </c>
+      <c r="F180">
+        <v>31.7</v>
+      </c>
+      <c r="G180">
+        <v>31.7</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>BEN-39DS-01-2021</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>122</v>
+      </c>
+      <c r="D181">
+        <v>58.9</v>
+      </c>
+      <c r="E181">
+        <v>86.8</v>
+      </c>
+      <c r="F181">
+        <v>29.5</v>
+      </c>
+      <c r="G181">
+        <v>29.5</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ANG-2023-07-01_bOPV</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>332</v>
+      </c>
+      <c r="D182">
+        <v>59.1</v>
+      </c>
+      <c r="E182">
+        <v>72.5</v>
+      </c>
+      <c r="F182">
+        <v>23.2</v>
+      </c>
+      <c r="G182">
+        <v>23.2</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>DRC-2026-03-NID_bOPV-Nopv</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>bOPV</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183">
+        <v>10</v>
+      </c>
+      <c r="E183">
+        <v>100</v>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Mekelle</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>12</v>
+      </c>
+      <c r="D184">
+        <v>381.7</v>
+      </c>
+      <c r="E184">
+        <v>68.7</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SSD-2024-02-01_nOPV</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>nOPV2</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>2</v>
+      </c>
+      <c r="D185">
+        <v>60</v>
+      </c>
+      <c r="E185">
+        <v>72.5</v>
+      </c>
+      <c r="F185">
+        <v>0</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2308,7 +8772,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 16:22:44</t>
+          <t>2026-09-02 00:20:16</t>
         </is>
       </c>
     </row>
@@ -2320,7 +8784,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -2344,7 +8808,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2356,7 +8820,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>ANG, GUI, NAM, NIE, GHA, ZMB, BEN, TOGO, CHD, RCA, BFA, CIV, RDC, COG, CAE, NIG, SSUD, LIB, SIL, SEN, KEN, MAU, UGA, ETH, GNB, MLW, TNZ, MOZ, ZIM, MDG, ALG, BWA, BUI, RWA</t>
         </is>
       </c>
     </row>
